--- a/data/combined_real_fake.xlsx
+++ b/data/combined_real_fake.xlsx
@@ -505,32 +505,32 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>Stemming</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Ch_length</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TQ</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SD_TQ</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Stemming</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Ch_length</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -629,22 +629,22 @@
         <v>6.75</v>
       </c>
       <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
         <v>35</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>3500</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>67.61234037828133</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>6.761234037828133</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2</v>
       </c>
       <c r="U2" t="n">
         <v>1.57401796720284</v>
@@ -726,22 +726,22 @@
         <v>7.875</v>
       </c>
       <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
         <v>35</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>3500</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>72.68326590665242</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>7.268326590665243</v>
-      </c>
-      <c r="S3" t="n">
-        <v>4</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>1.66392609771817</v>
@@ -823,22 +823,22 @@
         <v>9.125</v>
       </c>
       <c r="O4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
         <v>35</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>3500</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>81.13480845393759</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>8.113480845393759</v>
-      </c>
-      <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>2.586259144048288</v>
@@ -920,22 +920,22 @@
         <v>27</v>
       </c>
       <c r="O5" t="n">
+        <v>2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
         <v>35</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>1575</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>52.39956379316803</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>7.81126577552403</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>2.176795086935746</v>
@@ -1017,22 +1017,22 @@
         <v>10.63</v>
       </c>
       <c r="O6" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q6" t="n">
         <v>35</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>1575</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>54.08987230262506</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>8.063242090863515</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U6" t="n">
         <v>2.853015971352396</v>
@@ -1114,22 +1114,22 @@
         <v>6.25</v>
       </c>
       <c r="O7" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q7" t="n">
         <v>35</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>1575</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>76.06388292556649</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>11.33893419027682</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U7" t="n">
         <v>1.264973825883335</v>
@@ -1211,22 +1211,22 @@
         <v>24.63</v>
       </c>
       <c r="O8" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q8" t="n">
         <v>35</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>1575</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>30.4255531702266</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>4.535573676110727</v>
-      </c>
-      <c r="S8" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U8" t="n">
         <v>1.979621206397625</v>
@@ -1308,22 +1308,22 @@
         <v>28.88</v>
       </c>
       <c r="O9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
         <v>90</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>6300</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>26.3523138347365</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>3.14970394174356</v>
-      </c>
-      <c r="S9" t="n">
-        <v>4</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2</v>
       </c>
       <c r="U9" t="n">
         <v>0.6976370858327973</v>
@@ -1405,22 +1405,22 @@
         <v>14.25</v>
       </c>
       <c r="O10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
         <v>90</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>6300</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>29.51459149490487</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>3.527668414752787</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2</v>
       </c>
       <c r="U10" t="n">
         <v>1.464643327530867</v>
@@ -1502,22 +1502,22 @@
         <v>8.125</v>
       </c>
       <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
         <v>90</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>6300</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>31.62277660168379</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>3.779644730092272</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
       </c>
       <c r="U11" t="n">
         <v>1.084513364288608</v>
@@ -1599,22 +1599,22 @@
         <v>28.75</v>
       </c>
       <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
         <v>90</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>6300</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>45.32597979574677</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>5.417490779798924</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
       </c>
       <c r="U12" t="n">
         <v>1.155307632344655</v>
@@ -1696,22 +1696,22 @@
         <v>6.5</v>
       </c>
       <c r="O13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
         <v>25</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>2500</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>90</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>9</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>0.4928652983889979</v>
@@ -1793,22 +1793,22 @@
         <v>6</v>
       </c>
       <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
         <v>25</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>2500</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>86</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>8.6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
       </c>
       <c r="U14" t="n">
         <v>1.332629836534198</v>
@@ -1890,22 +1890,22 @@
         <v>6.25</v>
       </c>
       <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
         <v>25</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>2500</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>90</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>9</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>1.322555520152884</v>
@@ -1987,22 +1987,22 @@
         <v>10.63</v>
       </c>
       <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
         <v>25</v>
       </c>
-      <c r="P16" t="n">
+      <c r="R16" t="n">
         <v>2500</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>80</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
       </c>
       <c r="U16" t="n">
         <v>1.203272559211543</v>
@@ -2084,22 +2084,22 @@
         <v>5.75</v>
       </c>
       <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q17" t="n">
         <v>33</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>2970</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>78.33494518006403</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>8.257228238447704</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.5</v>
       </c>
       <c r="U17" t="n">
         <v>0.6037693694087286</v>
@@ -2181,22 +2181,22 @@
         <v>19.88</v>
       </c>
       <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q18" t="n">
         <v>33</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>2970</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>81.81649829917798</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>8.624216160156491</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.5</v>
       </c>
       <c r="U18" t="n">
         <v>0.4548899914356874</v>
@@ -2278,22 +2278,22 @@
         <v>7.625</v>
       </c>
       <c r="O19" t="n">
+        <v>3</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q19" t="n">
         <v>33</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>2970</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>73.11261550139309</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>7.706746355884524</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>1.5</v>
       </c>
       <c r="U19" t="n">
         <v>0.6010318916521397</v>
@@ -2375,22 +2375,22 @@
         <v>5.75</v>
       </c>
       <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q20" t="n">
         <v>33</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>2970</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>74.85339206095007</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>7.890240316738917</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.5</v>
       </c>
       <c r="U20" t="n">
         <v>0.6749832099322741</v>
@@ -2472,22 +2472,22 @@
         <v>5.75</v>
       </c>
       <c r="O21" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q21" t="n">
         <v>43</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>3440</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>77.77427086962838</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>8.695427828248537</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U21" t="n">
         <v>0.6825916666204287</v>
@@ -2569,22 +2569,22 @@
         <v>5.375</v>
       </c>
       <c r="O22" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q22" t="n">
         <v>43</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>3440</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>73.19931375965024</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>8.183932073645682</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U22" t="n">
         <v>0.8372475245337022</v>
@@ -2666,22 +2666,22 @@
         <v>3</v>
       </c>
       <c r="O23" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q23" t="n">
         <v>43</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>3440</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>70.14934235299815</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>7.842934903910446</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U23" t="n">
         <v>1.096610285997437</v>
@@ -2763,22 +2763,22 @@
         <v>2.75</v>
       </c>
       <c r="O24" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q24" t="n">
         <v>43</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>3440</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>65.57438524302</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>7.33143914930759</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U24" t="n">
         <v>1.621564092231941</v>
@@ -2860,22 +2860,22 @@
         <v>2.75</v>
       </c>
       <c r="O25" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q25" t="n">
         <v>43</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>3440</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>64.04939953969397</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>7.160940564439972</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U25" t="n">
         <v>1.998367051902165</v>
@@ -2957,22 +2957,22 @@
         <v>5.375</v>
       </c>
       <c r="O26" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q26" t="n">
         <v>50</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>5200</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>65.05382386916237</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>6.379052256590135</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U26" t="n">
         <v>0.5265021031509983</v>
@@ -3054,22 +3054,22 @@
         <v>3.375</v>
       </c>
       <c r="O27" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q27" t="n">
         <v>50</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>5200</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>67.88225099390856</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>6.65640235470275</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U27" t="n">
         <v>0.3030631744900834</v>
@@ -3151,22 +3151,22 @@
         <v>8.375</v>
       </c>
       <c r="O28" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q28" t="n">
         <v>50</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>5200</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>67.88225099390856</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>6.65640235470275</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U28" t="n">
         <v>0.3400373027857091</v>
@@ -3248,22 +3248,22 @@
         <v>4.75</v>
       </c>
       <c r="O29" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q29" t="n">
         <v>50</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>5200</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>66.46803743153546</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>6.517727305646442</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U29" t="n">
         <v>0.5247285289349821</v>
@@ -3345,22 +3345,22 @@
         <v>5.125</v>
       </c>
       <c r="O30" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q30" t="n">
         <v>50</v>
       </c>
-      <c r="P30" t="n">
+      <c r="R30" t="n">
         <v>5200</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>63.63961030678927</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>6.240377207533828</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U30" t="n">
         <v>0.5855619698800079</v>
@@ -3442,22 +3442,22 @@
         <v>4.125</v>
       </c>
       <c r="O31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
         <v>45</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>2700</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>71.55417527999327</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>9.237604307034012</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
       </c>
       <c r="U31" t="n">
         <v>1.213130742110702</v>
@@ -3539,22 +3539,22 @@
         <v>4.875</v>
       </c>
       <c r="O32" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q32" t="n">
         <v>45</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>2700</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>74.53559924999298</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>9.622504486493762</v>
-      </c>
-      <c r="S32" t="n">
-        <v>4</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
       </c>
       <c r="U32" t="n">
         <v>1.311840175194943</v>
@@ -3636,22 +3636,22 @@
         <v>5</v>
       </c>
       <c r="O33" t="n">
+        <v>4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q33" t="n">
         <v>45</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>2700</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>76.02631123499285</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>9.814954576223638</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
       </c>
       <c r="U33" t="n">
         <v>1.124280035416687</v>
@@ -3733,22 +3733,22 @@
         <v>7.125</v>
       </c>
       <c r="O34" t="n">
+        <v>4</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q34" t="n">
         <v>45</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>2700</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>73.04488726499312</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>9.430054396763888</v>
-      </c>
-      <c r="S34" t="n">
-        <v>4</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
       </c>
       <c r="U34" t="n">
         <v>1.338153985791956</v>
@@ -3830,22 +3830,22 @@
         <v>5</v>
       </c>
       <c r="O35" t="n">
+        <v>4</v>
+      </c>
+      <c r="P35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" t="n">
         <v>45</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>2700</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>70.06346329499341</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>9.045154217304137</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
       </c>
       <c r="U35" t="n">
         <v>1.476591999100671</v>
@@ -3927,22 +3927,22 @@
         <v>5.625</v>
       </c>
       <c r="O36" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q36" t="n">
         <v>25</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>3000</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>76</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>6.937819061732104</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U36" t="n">
         <v>1.748677979525604</v>
@@ -4024,22 +4024,22 @@
         <v>7.75</v>
       </c>
       <c r="O37" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q37" t="n">
         <v>25</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>3000</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>84</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>7.668115805072325</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U37" t="n">
         <v>1.522135584031304</v>
@@ -4121,22 +4121,22 @@
         <v>7.625</v>
       </c>
       <c r="O38" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q38" t="n">
         <v>25</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>3000</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>88</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>8.033264176742437</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U38" t="n">
         <v>1.957415140669637</v>
@@ -4218,22 +4218,22 @@
         <v>9.875</v>
       </c>
       <c r="O39" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q39" t="n">
         <v>25</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>3000</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>94</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>8.580986734247602</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U39" t="n">
         <v>1.633154439051417</v>
@@ -4315,22 +4315,22 @@
         <v>8</v>
       </c>
       <c r="O40" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q40" t="n">
         <v>25</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>3000</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>80</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>7.302967433402214</v>
-      </c>
-      <c r="S40" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U40" t="n">
         <v>1.19543647330365</v>
@@ -4412,22 +4412,22 @@
         <v>5.875</v>
       </c>
       <c r="O41" t="n">
+        <v>4</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" t="n">
         <v>35</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>5600</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="S41" t="n">
         <v>81.13480845393759</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>6.414269805898185</v>
-      </c>
-      <c r="S41" t="n">
-        <v>4</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>0.5799784824543073</v>
@@ -4509,22 +4509,22 @@
         <v>5.5</v>
       </c>
       <c r="O42" t="n">
+        <v>4</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" t="n">
         <v>35</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>5600</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="S42" t="n">
         <v>82.82511696339462</v>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>6.547900426854397</v>
-      </c>
-      <c r="S42" t="n">
-        <v>4</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0.4074631107708374</v>
@@ -4606,22 +4606,22 @@
         <v>8.5</v>
       </c>
       <c r="O43" t="n">
+        <v>4</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" t="n">
         <v>35</v>
       </c>
-      <c r="P43" t="n">
+      <c r="R43" t="n">
         <v>5600</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="S43" t="n">
         <v>87.89604249176573</v>
       </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>6.948792289723033</v>
-      </c>
-      <c r="S43" t="n">
-        <v>4</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2</v>
       </c>
       <c r="U43" t="n">
         <v>0.5647454657554211</v>
@@ -4703,22 +4703,22 @@
         <v>6.25</v>
       </c>
       <c r="O44" t="n">
+        <v>4</v>
+      </c>
+      <c r="P44" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q44" t="n">
         <v>35</v>
       </c>
-      <c r="P44" t="n">
+      <c r="R44" t="n">
         <v>5600</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="S44" t="n">
         <v>91.27665951067979</v>
       </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
         <v>7.216053531635458</v>
-      </c>
-      <c r="S44" t="n">
-        <v>4</v>
-      </c>
-      <c r="T44" t="n">
-        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0.5704144151776482</v>
@@ -4800,22 +4800,22 @@
         <v>5.375</v>
       </c>
       <c r="O45" t="n">
+        <v>4</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q45" t="n">
         <v>35</v>
       </c>
-      <c r="P45" t="n">
+      <c r="R45" t="n">
         <v>5600</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="S45" t="n">
         <v>84.51542547285166</v>
       </c>
-      <c r="R45" t="n">
+      <c r="T45" t="n">
         <v>6.681531047810609</v>
-      </c>
-      <c r="S45" t="n">
-        <v>4</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2</v>
       </c>
       <c r="U45" t="n">
         <v>0.946625931670228</v>
@@ -4895,22 +4895,22 @@
         <v>3.73</v>
       </c>
       <c r="O46" t="n">
+        <v>3.733333333333333</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.866666666666666</v>
+      </c>
+      <c r="Q46" t="n">
         <v>47.5</v>
       </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
         <v>4037.5</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="S46" t="n">
         <v>59.34395725899896</v>
       </c>
-      <c r="R46" t="n">
+      <c r="T46" t="n">
         <v>6.436755908482704</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.733333333333333</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1.866666666666666</v>
       </c>
       <c r="U46" t="n">
         <v>0.6714126884139392</v>
@@ -4922,7 +4922,7 @@
         <v>1.862024672277346</v>
       </c>
       <c r="X46" t="n">
-        <v>6.013715156042802</v>
+        <v>6.013715156042801</v>
       </c>
       <c r="Y46" t="n">
         <v>3.860729711040595</v>
@@ -4990,22 +4990,22 @@
         <v>6.15</v>
       </c>
       <c r="O47" t="n">
+        <v>3</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q47" t="n">
         <v>48.1</v>
       </c>
-      <c r="P47" t="n">
+      <c r="R47" t="n">
         <v>3511.3</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="S47" t="n">
         <v>72.5262874416054</v>
       </c>
-      <c r="R47" t="n">
+      <c r="T47" t="n">
         <v>8.488559884041814</v>
-      </c>
-      <c r="S47" t="n">
-        <v>3</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1.5</v>
       </c>
       <c r="U47" t="n">
         <v>0.1578580846155803</v>
@@ -5085,22 +5085,22 @@
         <v>25.31</v>
       </c>
       <c r="O48" t="n">
+        <v>3.399999999999999</v>
+      </c>
+      <c r="P48" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q48" t="n">
         <v>43.3</v>
       </c>
-      <c r="P48" t="n">
+      <c r="R48" t="n">
         <v>2727.9</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="S48" t="n">
         <v>63.97910311268771</v>
       </c>
-      <c r="R48" t="n">
+      <c r="T48" t="n">
         <v>8.060609330530006</v>
-      </c>
-      <c r="S48" t="n">
-        <v>3.399999999999999</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1.7</v>
       </c>
       <c r="U48" t="n">
         <v>0.5423242908253617</v>
@@ -5180,22 +5180,22 @@
         <v>4.14</v>
       </c>
       <c r="O49" t="n">
+        <v>2.933333333333334</v>
+      </c>
+      <c r="P49" t="n">
+        <v>1.466666666666667</v>
+      </c>
+      <c r="Q49" t="n">
         <v>54.2</v>
       </c>
-      <c r="P49" t="n">
+      <c r="R49" t="n">
         <v>5420</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="S49" t="n">
         <v>68.45905394044432</v>
       </c>
-      <c r="R49" t="n">
+      <c r="T49" t="n">
         <v>6.845905394044431</v>
-      </c>
-      <c r="S49" t="n">
-        <v>2.933333333333334</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1.466666666666667</v>
       </c>
       <c r="U49" t="n">
         <v>0.3118867611485984</v>
@@ -5275,22 +5275,22 @@
         <v>5.08</v>
       </c>
       <c r="O50" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q50" t="n">
         <v>43.3</v>
       </c>
-      <c r="P50" t="n">
+      <c r="R50" t="n">
         <v>5196</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="S50" t="n">
         <v>58.05229783621545</v>
       </c>
-      <c r="R50" t="n">
+      <c r="T50" t="n">
         <v>5.299425506650592</v>
-      </c>
-      <c r="S50" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U50" t="n">
         <v>0.8919980393051105</v>
@@ -5370,22 +5370,22 @@
         <v>5.48</v>
       </c>
       <c r="O51" t="n">
+        <v>3.866666666666666</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.933333333333333</v>
+      </c>
+      <c r="Q51" t="n">
         <v>53.3</v>
       </c>
-      <c r="P51" t="n">
+      <c r="R51" t="n">
         <v>6449.299999999999</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="S51" t="n">
         <v>63.00778712408429</v>
       </c>
-      <c r="R51" t="n">
+      <c r="T51" t="n">
         <v>5.727980647644026</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.866666666666666</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1.933333333333333</v>
       </c>
       <c r="U51" t="n">
         <v>0.8389776287714849</v>
@@ -5465,22 +5465,22 @@
         <v>14.29</v>
       </c>
       <c r="O52" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="P52" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="Q52" t="n">
         <v>54.3</v>
       </c>
-      <c r="P52" t="n">
+      <c r="R52" t="n">
         <v>8145</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="S52" t="n">
         <v>57.40377487731749</v>
       </c>
-      <c r="R52" t="n">
+      <c r="T52" t="n">
         <v>4.686998591967462</v>
-      </c>
-      <c r="S52" t="n">
-        <v>3.666666666666667</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1.833333333333333</v>
       </c>
       <c r="U52" t="n">
         <v>0.779783487219492</v>
@@ -5560,22 +5560,22 @@
         <v>4.58</v>
       </c>
       <c r="O53" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1.633333333333333</v>
+      </c>
+      <c r="Q53" t="n">
         <v>25.5</v>
       </c>
-      <c r="P53" t="n">
+      <c r="R53" t="n">
         <v>2422.5</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="S53" t="n">
         <v>90.49948542806804</v>
       </c>
-      <c r="R53" t="n">
+      <c r="T53" t="n">
         <v>9.285051292404367</v>
-      </c>
-      <c r="S53" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1.633333333333333</v>
       </c>
       <c r="U53" t="n">
         <v>-0.03355678352884275</v>
@@ -5655,22 +5655,22 @@
         <v>20.61</v>
       </c>
       <c r="O54" t="n">
+        <v>3.933333333333334</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.966666666666667</v>
+      </c>
+      <c r="Q54" t="n">
         <v>27.9</v>
       </c>
-      <c r="P54" t="n">
+      <c r="R54" t="n">
         <v>2008.8</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="S54" t="n">
         <v>90.11661103386761</v>
       </c>
-      <c r="R54" t="n">
+      <c r="T54" t="n">
         <v>10.62034445993304</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3.933333333333334</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1.966666666666667</v>
       </c>
       <c r="U54" t="n">
         <v>0.126632650933366</v>
@@ -5750,22 +5750,22 @@
         <v>4.48</v>
       </c>
       <c r="O55" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P55" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q55" t="n">
         <v>46.9</v>
       </c>
-      <c r="P55" t="n">
+      <c r="R55" t="n">
         <v>1969.8</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="S55" t="n">
         <v>48.3327573918581</v>
       </c>
-      <c r="R55" t="n">
+      <c r="T55" t="n">
         <v>7.457906378468764</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U55" t="n">
         <v>1.198759237273048</v>
@@ -5780,7 +5780,7 @@
         <v>5.802118375377063</v>
       </c>
       <c r="Y55" t="n">
-        <v>3.848017675452234</v>
+        <v>3.848017675452233</v>
       </c>
       <c r="Z55" t="n">
         <v>7.585687293735602</v>
@@ -5845,22 +5845,22 @@
         <v>6.74</v>
       </c>
       <c r="O56" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q56" t="n">
         <v>25.9</v>
       </c>
-      <c r="P56" t="n">
+      <c r="R56" t="n">
         <v>3600.1</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="S56" t="n">
         <v>67.00458118378101</v>
       </c>
-      <c r="R56" t="n">
+      <c r="T56" t="n">
         <v>5.683254399792594</v>
-      </c>
-      <c r="S56" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T56" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U56" t="n">
         <v>0.6729444732424258</v>
@@ -5940,22 +5940,22 @@
         <v>15.5</v>
       </c>
       <c r="O57" t="n">
+        <v>3.066666666666666</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="Q57" t="n">
         <v>36.1</v>
       </c>
-      <c r="P57" t="n">
+      <c r="R57" t="n">
         <v>2490.9</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="S57" t="n">
         <v>88.71021015103926</v>
       </c>
-      <c r="R57" t="n">
+      <c r="T57" t="n">
         <v>10.67945432645073</v>
-      </c>
-      <c r="S57" t="n">
-        <v>3.066666666666666</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1.533333333333333</v>
       </c>
       <c r="U57" t="n">
         <v>0.3249778571954777</v>
@@ -6035,22 +6035,22 @@
         <v>5.66</v>
       </c>
       <c r="O58" t="n">
+        <v>2.733333333333333</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1.366666666666666</v>
+      </c>
+      <c r="Q58" t="n">
         <v>61.1</v>
       </c>
-      <c r="P58" t="n">
+      <c r="R58" t="n">
         <v>8431.800000000001</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="S58" t="n">
         <v>65.62914705157196</v>
       </c>
-      <c r="R58" t="n">
+      <c r="T58" t="n">
         <v>5.586724003577691</v>
-      </c>
-      <c r="S58" t="n">
-        <v>2.733333333333333</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1.366666666666666</v>
       </c>
       <c r="U58" t="n">
         <v>0.62057648772511</v>
@@ -6130,25 +6130,25 @@
         <v>4.58</v>
       </c>
       <c r="O59" t="n">
+        <v>2.533333333333333</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="Q59" t="n">
         <v>34.5</v>
       </c>
-      <c r="P59" t="n">
+      <c r="R59" t="n">
         <v>3864</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="S59" t="n">
         <v>61.2904702146299</v>
       </c>
-      <c r="R59" t="n">
+      <c r="T59" t="n">
         <v>5.791405068790081</v>
       </c>
-      <c r="S59" t="n">
-        <v>2.533333333333333</v>
-      </c>
-      <c r="T59" t="n">
-        <v>1.266666666666667</v>
-      </c>
       <c r="U59" t="n">
-        <v>0.6575200029167942</v>
+        <v>0.6575200029167941</v>
       </c>
       <c r="V59" t="n">
         <v>4.115624369431499</v>
@@ -6225,25 +6225,25 @@
         <v>18.02</v>
       </c>
       <c r="O60" t="n">
+        <v>2.266666666666667</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="Q60" t="n">
         <v>43.4</v>
       </c>
-      <c r="P60" t="n">
+      <c r="R60" t="n">
         <v>5859</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="S60" t="n">
         <v>75.89709258986454</v>
       </c>
-      <c r="R60" t="n">
+      <c r="T60" t="n">
         <v>6.532181680580171</v>
       </c>
-      <c r="S60" t="n">
-        <v>2.266666666666667</v>
-      </c>
-      <c r="T60" t="n">
-        <v>1.133333333333333</v>
-      </c>
       <c r="U60" t="n">
-        <v>0.5205779152086689</v>
+        <v>0.520577915208669</v>
       </c>
       <c r="V60" t="n">
         <v>4.329378377869012</v>
@@ -6320,22 +6320,22 @@
         <v>7.95</v>
       </c>
       <c r="O61" t="n">
+        <v>3.866666666666666</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1.933333333333333</v>
+      </c>
+      <c r="Q61" t="n">
         <v>58.3</v>
       </c>
-      <c r="P61" t="n">
+      <c r="R61" t="n">
         <v>5655.099999999999</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="S61" t="n">
         <v>42.30271534496883</v>
       </c>
-      <c r="R61" t="n">
+      <c r="T61" t="n">
         <v>4.295189980025321</v>
-      </c>
-      <c r="S61" t="n">
-        <v>3.866666666666666</v>
-      </c>
-      <c r="T61" t="n">
-        <v>1.933333333333333</v>
       </c>
       <c r="U61" t="n">
         <v>1.346253311582707</v>
@@ -6415,22 +6415,22 @@
         <v>20.31</v>
       </c>
       <c r="O62" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q62" t="n">
         <v>51.5</v>
       </c>
-      <c r="P62" t="n">
+      <c r="R62" t="n">
         <v>6901</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="S62" t="n">
         <v>61.73054506623733</v>
       </c>
-      <c r="R62" t="n">
+      <c r="T62" t="n">
         <v>5.332706877664964</v>
-      </c>
-      <c r="S62" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T62" t="n">
-        <v>1.8</v>
       </c>
       <c r="U62" t="n">
         <v>0.2768738737351775</v>
@@ -6510,22 +6510,22 @@
         <v>25.07</v>
       </c>
       <c r="O63" t="n">
+        <v>4.133333333333333</v>
+      </c>
+      <c r="P63" t="n">
+        <v>2.066666666666666</v>
+      </c>
+      <c r="Q63" t="n">
         <v>27.3</v>
       </c>
-      <c r="P63" t="n">
+      <c r="R63" t="n">
         <v>3740.1</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="S63" t="n">
         <v>107.7524295808966</v>
       </c>
-      <c r="R63" t="n">
+      <c r="T63" t="n">
         <v>9.205911335002504</v>
-      </c>
-      <c r="S63" t="n">
-        <v>4.133333333333333</v>
-      </c>
-      <c r="T63" t="n">
-        <v>2.066666666666666</v>
       </c>
       <c r="U63" t="n">
         <v>-0.007024614936964466</v>
@@ -6537,7 +6537,7 @@
         <v>2.219845814130171</v>
       </c>
       <c r="X63" t="n">
-        <v>6.333279628139691</v>
+        <v>6.33327962813969</v>
       </c>
       <c r="Y63" t="n">
         <v>3.306886702190914</v>
@@ -6605,22 +6605,22 @@
         <v>5</v>
       </c>
       <c r="O64" t="n">
+        <v>3.733333333333333</v>
+      </c>
+      <c r="P64" t="n">
+        <v>1.866666666666666</v>
+      </c>
+      <c r="Q64" t="n">
         <v>49.1</v>
       </c>
-      <c r="P64" t="n">
+      <c r="R64" t="n">
         <v>3780.7</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="S64" t="n">
         <v>62.07954295714347</v>
       </c>
-      <c r="R64" t="n">
+      <c r="T64" t="n">
         <v>7.074620501746926</v>
-      </c>
-      <c r="S64" t="n">
-        <v>3.733333333333333</v>
-      </c>
-      <c r="T64" t="n">
-        <v>1.866666666666666</v>
       </c>
       <c r="U64" t="n">
         <v>0.7366854825744287</v>
@@ -6700,22 +6700,22 @@
         <v>12.2</v>
       </c>
       <c r="O65" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q65" t="n">
         <v>25</v>
       </c>
-      <c r="P65" t="n">
+      <c r="R65" t="n">
         <v>2400</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="S65" t="n">
         <v>105</v>
       </c>
-      <c r="R65" t="n">
+      <c r="T65" t="n">
         <v>10.7165176246764</v>
-      </c>
-      <c r="S65" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T65" t="n">
-        <v>1.8</v>
       </c>
       <c r="U65" t="n">
         <v>-0.02942881069081217</v>
@@ -6795,25 +6795,25 @@
         <v>10.9</v>
       </c>
       <c r="O66" t="n">
+        <v>2.266666666666667</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="Q66" t="n">
         <v>25</v>
       </c>
-      <c r="P66" t="n">
+      <c r="R66" t="n">
         <v>2650</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="S66" t="n">
         <v>89.59999999999999</v>
       </c>
-      <c r="R66" t="n">
+      <c r="T66" t="n">
         <v>8.702721326721086</v>
       </c>
-      <c r="S66" t="n">
-        <v>2.266666666666667</v>
-      </c>
-      <c r="T66" t="n">
-        <v>1.133333333333333</v>
-      </c>
       <c r="U66" t="n">
-        <v>0.2255406759139312</v>
+        <v>0.2255406759139311</v>
       </c>
       <c r="V66" t="n">
         <v>4.495355319980884</v>
@@ -6890,22 +6890,22 @@
         <v>2.75</v>
       </c>
       <c r="O67" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q67" t="n">
         <v>42.6</v>
       </c>
-      <c r="P67" t="n">
+      <c r="R67" t="n">
         <v>2087.4</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="S67" t="n">
         <v>97.74980037922535</v>
       </c>
-      <c r="R67" t="n">
+      <c r="T67" t="n">
         <v>13.96425719703219</v>
-      </c>
-      <c r="S67" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T67" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U67" t="n">
         <v>-0.348140041488895</v>
@@ -6985,22 +6985,22 @@
         <v>8.720000000000001</v>
       </c>
       <c r="O68" t="n">
+        <v>3</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q68" t="n">
         <v>25</v>
       </c>
-      <c r="P68" t="n">
+      <c r="R68" t="n">
         <v>2600</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="S68" t="n">
         <v>95.40000000000001</v>
       </c>
-      <c r="R68" t="n">
+      <c r="T68" t="n">
         <v>9.354739646091378</v>
-      </c>
-      <c r="S68" t="n">
-        <v>3</v>
-      </c>
-      <c r="T68" t="n">
-        <v>1.5</v>
       </c>
       <c r="U68" t="n">
         <v>0.07696104113612839</v>
@@ -7080,22 +7080,22 @@
         <v>3.86</v>
       </c>
       <c r="O69" t="n">
+        <v>3.066666666666666</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="Q69" t="n">
         <v>32.7</v>
       </c>
-      <c r="P69" t="n">
+      <c r="R69" t="n">
         <v>4741.5</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="S69" t="n">
         <v>103.1758689754437</v>
       </c>
-      <c r="R69" t="n">
+      <c r="T69" t="n">
         <v>8.568289548392324</v>
-      </c>
-      <c r="S69" t="n">
-        <v>3.066666666666666</v>
-      </c>
-      <c r="T69" t="n">
-        <v>1.533333333333333</v>
       </c>
       <c r="U69" t="n">
         <v>-0.1450257720502577</v>
@@ -7107,7 +7107,7 @@
         <v>2.148068126737874</v>
       </c>
       <c r="X69" t="n">
-        <v>6.380122536899765</v>
+        <v>6.380122536899766</v>
       </c>
       <c r="Y69" t="n">
         <v>3.487375077903208</v>
@@ -7175,22 +7175,22 @@
         <v>6.02</v>
       </c>
       <c r="O70" t="n">
+        <v>3.533333333333333</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1.766666666666667</v>
+      </c>
+      <c r="Q70" t="n">
         <v>35.2</v>
       </c>
-      <c r="P70" t="n">
+      <c r="R70" t="n">
         <v>2886.4</v>
       </c>
-      <c r="Q70" t="n">
+      <c r="S70" t="n">
         <v>101.6356292663337</v>
       </c>
-      <c r="R70" t="n">
+      <c r="T70" t="n">
         <v>11.22377764345857</v>
-      </c>
-      <c r="S70" t="n">
-        <v>3.533333333333333</v>
-      </c>
-      <c r="T70" t="n">
-        <v>1.766666666666667</v>
       </c>
       <c r="U70" t="n">
         <v>-0.05657035148839435</v>
@@ -7270,22 +7270,22 @@
         <v>8.1</v>
       </c>
       <c r="O71" t="n">
+        <v>3.733333333333333</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1.866666666666666</v>
+      </c>
+      <c r="Q71" t="n">
         <v>27.8</v>
       </c>
-      <c r="P71" t="n">
+      <c r="R71" t="n">
         <v>3169.2</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="S71" t="n">
         <v>76.05398499154087</v>
       </c>
-      <c r="R71" t="n">
+      <c r="T71" t="n">
         <v>7.123108325732428</v>
-      </c>
-      <c r="S71" t="n">
-        <v>3.733333333333333</v>
-      </c>
-      <c r="T71" t="n">
-        <v>1.866666666666666</v>
       </c>
       <c r="U71" t="n">
         <v>0.5031965966014995</v>
@@ -7365,25 +7365,25 @@
         <v>7.4</v>
       </c>
       <c r="O72" t="n">
+        <v>3.733333333333333</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1.866666666666666</v>
+      </c>
+      <c r="Q72" t="n">
         <v>69</v>
       </c>
-      <c r="P72" t="n">
+      <c r="R72" t="n">
         <v>7176</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="S72" t="n">
         <v>57.54443777499768</v>
       </c>
-      <c r="R72" t="n">
+      <c r="T72" t="n">
         <v>5.642696367566133</v>
       </c>
-      <c r="S72" t="n">
-        <v>3.733333333333333</v>
-      </c>
-      <c r="T72" t="n">
-        <v>1.866666666666666</v>
-      </c>
       <c r="U72" t="n">
-        <v>0.8812851226753398</v>
+        <v>0.8812851226753399</v>
       </c>
       <c r="V72" t="n">
         <v>4.052557480192826</v>
@@ -7460,25 +7460,25 @@
         <v>3.09</v>
       </c>
       <c r="O73" t="n">
+        <v>4.066666666666666</v>
+      </c>
+      <c r="P73" t="n">
+        <v>2.033333333333333</v>
+      </c>
+      <c r="Q73" t="n">
         <v>57</v>
       </c>
-      <c r="P73" t="n">
+      <c r="R73" t="n">
         <v>6099</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="S73" t="n">
         <v>51.92166839694972</v>
       </c>
-      <c r="R73" t="n">
+      <c r="T73" t="n">
         <v>5.019457141146036</v>
       </c>
-      <c r="S73" t="n">
-        <v>4.066666666666666</v>
-      </c>
-      <c r="T73" t="n">
-        <v>2.033333333333333</v>
-      </c>
       <c r="U73" t="n">
-        <v>0.9262410627273232</v>
+        <v>0.9262410627273231</v>
       </c>
       <c r="V73" t="n">
         <v>3.949736205873188</v>
@@ -7555,22 +7555,22 @@
         <v>6.83</v>
       </c>
       <c r="O74" t="n">
+        <v>2.533333333333333</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="Q74" t="n">
         <v>63.3</v>
       </c>
-      <c r="P74" t="n">
+      <c r="R74" t="n">
         <v>3481.5</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="S74" t="n">
         <v>53.54362176094946</v>
       </c>
-      <c r="R74" t="n">
+      <c r="T74" t="n">
         <v>7.219820485403197</v>
-      </c>
-      <c r="S74" t="n">
-        <v>2.533333333333333</v>
-      </c>
-      <c r="T74" t="n">
-        <v>1.266666666666667</v>
       </c>
       <c r="U74" t="n">
         <v>0.7414610408384961</v>
@@ -7582,7 +7582,7 @@
         <v>1.97683008907807</v>
       </c>
       <c r="X74" t="n">
-        <v>6.054439346269371</v>
+        <v>6.05443934626937</v>
       </c>
       <c r="Y74" t="n">
         <v>4.147885329150131</v>
@@ -7650,22 +7650,22 @@
         <v>6.98</v>
       </c>
       <c r="O75" t="n">
+        <v>3.733333333333333</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1.866666666666666</v>
+      </c>
+      <c r="Q75" t="n">
         <v>31.6</v>
       </c>
-      <c r="P75" t="n">
+      <c r="R75" t="n">
         <v>3665.6</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="S75" t="n">
         <v>65.82004619424585</v>
       </c>
-      <c r="R75" t="n">
+      <c r="T75" t="n">
         <v>6.111237868434829</v>
-      </c>
-      <c r="S75" t="n">
-        <v>3.733333333333333</v>
-      </c>
-      <c r="T75" t="n">
-        <v>1.866666666666666</v>
       </c>
       <c r="U75" t="n">
         <v>0.8060293376166178</v>
@@ -7677,7 +7677,7 @@
         <v>1.810129349788655</v>
       </c>
       <c r="X75" t="n">
-        <v>5.91350300563827</v>
+        <v>5.913503005638271</v>
       </c>
       <c r="Y75" t="n">
         <v>3.453157120592866</v>
@@ -7745,22 +7745,22 @@
         <v>2.59</v>
       </c>
       <c r="O76" t="n">
+        <v>3.733333333333333</v>
+      </c>
+      <c r="P76" t="n">
+        <v>1.866666666666666</v>
+      </c>
+      <c r="Q76" t="n">
         <v>27.1</v>
       </c>
-      <c r="P76" t="n">
+      <c r="R76" t="n">
         <v>3170.7</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="S76" t="n">
         <v>81.25605285430282</v>
       </c>
-      <c r="R76" t="n">
+      <c r="T76" t="n">
         <v>7.512124743794894</v>
-      </c>
-      <c r="S76" t="n">
-        <v>3.733333333333333</v>
-      </c>
-      <c r="T76" t="n">
-        <v>1.866666666666666</v>
       </c>
       <c r="U76" t="n">
         <v>0.2421615571499716</v>
@@ -7840,22 +7840,22 @@
         <v>13.67</v>
       </c>
       <c r="O77" t="n">
+        <v>3.533333333333333</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1.766666666666667</v>
+      </c>
+      <c r="Q77" t="n">
         <v>54.8</v>
       </c>
-      <c r="P77" t="n">
+      <c r="R77" t="n">
         <v>5096.4</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="S77" t="n">
         <v>60.51844141932951</v>
       </c>
-      <c r="R77" t="n">
+      <c r="T77" t="n">
         <v>6.27547003922177</v>
-      </c>
-      <c r="S77" t="n">
-        <v>3.533333333333333</v>
-      </c>
-      <c r="T77" t="n">
-        <v>1.766666666666667</v>
       </c>
       <c r="U77" t="n">
         <v>0.5754891370917129</v>
@@ -7935,22 +7935,22 @@
         <v>6.54</v>
       </c>
       <c r="O78" t="n">
+        <v>3.533333333333333</v>
+      </c>
+      <c r="P78" t="n">
+        <v>1.766666666666667</v>
+      </c>
+      <c r="Q78" t="n">
         <v>34.9</v>
       </c>
-      <c r="P78" t="n">
+      <c r="R78" t="n">
         <v>3420.2</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="S78" t="n">
         <v>80.40460007653199</v>
       </c>
-      <c r="R78" t="n">
+      <c r="T78" t="n">
         <v>8.122091136101167</v>
-      </c>
-      <c r="S78" t="n">
-        <v>3.533333333333333</v>
-      </c>
-      <c r="T78" t="n">
-        <v>1.766666666666667</v>
       </c>
       <c r="U78" t="n">
         <v>0.2468600779315258</v>
@@ -8030,22 +8030,22 @@
         <v>7.06</v>
       </c>
       <c r="O79" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q79" t="n">
         <v>43.5</v>
       </c>
-      <c r="P79" t="n">
+      <c r="R79" t="n">
         <v>1740</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="S79" t="n">
         <v>37.45004335279783</v>
       </c>
-      <c r="R79" t="n">
+      <c r="T79" t="n">
         <v>5.921371773344494</v>
-      </c>
-      <c r="S79" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T79" t="n">
-        <v>1.2</v>
       </c>
       <c r="U79" t="n">
         <v>1.655175804107954</v>
@@ -8125,22 +8125,22 @@
         <v>3.19</v>
       </c>
       <c r="O80" t="n">
+        <v>3.533333333333333</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1.766666666666667</v>
+      </c>
+      <c r="Q80" t="n">
         <v>39.7</v>
       </c>
-      <c r="P80" t="n">
+      <c r="R80" t="n">
         <v>3136.3</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="S80" t="n">
         <v>90.14737443979114</v>
       </c>
-      <c r="R80" t="n">
+      <c r="T80" t="n">
         <v>10.14237202824569</v>
-      </c>
-      <c r="S80" t="n">
-        <v>3.533333333333333</v>
-      </c>
-      <c r="T80" t="n">
-        <v>1.766666666666667</v>
       </c>
       <c r="U80" t="n">
         <v>0.2151113796169455</v>
@@ -8220,25 +8220,25 @@
         <v>2.87</v>
       </c>
       <c r="O81" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q81" t="n">
         <v>40.2</v>
       </c>
-      <c r="P81" t="n">
+      <c r="R81" t="n">
         <v>3738.6</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="S81" t="n">
         <v>61.66854911742902</v>
       </c>
-      <c r="R81" t="n">
+      <c r="T81" t="n">
         <v>6.39473065188845</v>
       </c>
-      <c r="S81" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T81" t="n">
-        <v>1.4</v>
-      </c>
       <c r="U81" t="n">
-        <v>0.9947321581807178</v>
+        <v>0.9947321581807177</v>
       </c>
       <c r="V81" t="n">
         <v>4.121774062172879</v>
@@ -8250,7 +8250,7 @@
         <v>5.968707559985366</v>
       </c>
       <c r="Y81" t="n">
-        <v>3.693866995624976</v>
+        <v>3.693866995624975</v>
       </c>
       <c r="Z81" t="n">
         <v>8.226466488778231</v>
@@ -8315,22 +8315,22 @@
         <v>31.82</v>
       </c>
       <c r="O82" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q82" t="n">
         <v>26.9</v>
       </c>
-      <c r="P82" t="n">
+      <c r="R82" t="n">
         <v>2178.9</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="S82" t="n">
         <v>110.4786813528169</v>
       </c>
-      <c r="R82" t="n">
+      <c r="T82" t="n">
         <v>12.27540903920188</v>
-      </c>
-      <c r="S82" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T82" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U82" t="n">
         <v>-0.05129329438755058</v>
@@ -8410,22 +8410,22 @@
         <v>18.58</v>
       </c>
       <c r="O83" t="n">
+        <v>2.933333333333334</v>
+      </c>
+      <c r="P83" t="n">
+        <v>1.466666666666667</v>
+      </c>
+      <c r="Q83" t="n">
         <v>68.09999999999999</v>
       </c>
-      <c r="P83" t="n">
+      <c r="R83" t="n">
         <v>8376.299999999999</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="S83" t="n">
         <v>60.22583538785049</v>
       </c>
-      <c r="R83" t="n">
+      <c r="T83" t="n">
         <v>5.430380699170406</v>
-      </c>
-      <c r="S83" t="n">
-        <v>2.933333333333334</v>
-      </c>
-      <c r="T83" t="n">
-        <v>1.466666666666667</v>
       </c>
       <c r="U83" t="n">
         <v>0.9764446546939021</v>
@@ -8505,22 +8505,22 @@
         <v>7.56</v>
       </c>
       <c r="O84" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="P84" t="n">
+        <v>1.633333333333333</v>
+      </c>
+      <c r="Q84" t="n">
         <v>35.4</v>
       </c>
-      <c r="P84" t="n">
+      <c r="R84" t="n">
         <v>1734.6</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="S84" t="n">
         <v>93.95289720203081</v>
       </c>
-      <c r="R84" t="n">
+      <c r="T84" t="n">
         <v>13.42184245743297</v>
-      </c>
-      <c r="S84" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="T84" t="n">
-        <v>1.633333333333333</v>
       </c>
       <c r="U84" t="n">
         <v>0.154436353304419</v>
@@ -8600,22 +8600,22 @@
         <v>4.82</v>
       </c>
       <c r="O85" t="n">
+        <v>3.466666666666667</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1.733333333333333</v>
+      </c>
+      <c r="Q85" t="n">
         <v>32.7</v>
       </c>
-      <c r="P85" t="n">
+      <c r="R85" t="n">
         <v>4806.900000000001</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="S85" t="n">
         <v>65.05325976078822</v>
       </c>
-      <c r="R85" t="n">
+      <c r="T85" t="n">
         <v>5.365502433507674</v>
-      </c>
-      <c r="S85" t="n">
-        <v>3.466666666666667</v>
-      </c>
-      <c r="T85" t="n">
-        <v>1.733333333333333</v>
       </c>
       <c r="U85" t="n">
         <v>0.8505781885087738</v>
@@ -8695,22 +8695,22 @@
         <v>5.44</v>
       </c>
       <c r="O86" t="n">
+        <v>4.066666666666666</v>
+      </c>
+      <c r="P86" t="n">
+        <v>2.033333333333333</v>
+      </c>
+      <c r="Q86" t="n">
         <v>25</v>
       </c>
-      <c r="P86" t="n">
+      <c r="R86" t="n">
         <v>2700</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="S86" t="n">
         <v>80.59999999999999</v>
       </c>
-      <c r="R86" t="n">
+      <c r="T86" t="n">
         <v>7.755738616113972</v>
-      </c>
-      <c r="S86" t="n">
-        <v>4.066666666666666</v>
-      </c>
-      <c r="T86" t="n">
-        <v>2.033333333333333</v>
       </c>
       <c r="U86" t="n">
         <v>0.6481498146292095</v>
@@ -8790,22 +8790,22 @@
         <v>9.99</v>
       </c>
       <c r="O87" t="n">
+        <v>4</v>
+      </c>
+      <c r="P87" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q87" t="n">
         <v>66.3</v>
       </c>
-      <c r="P87" t="n">
+      <c r="R87" t="n">
         <v>5370.3</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="S87" t="n">
         <v>48.01976088963205</v>
       </c>
-      <c r="R87" t="n">
+      <c r="T87" t="n">
         <v>5.335528987736894</v>
-      </c>
-      <c r="S87" t="n">
-        <v>4</v>
-      </c>
-      <c r="T87" t="n">
-        <v>2</v>
       </c>
       <c r="U87" t="n">
         <v>0.9936220748104786</v>
@@ -8885,22 +8885,22 @@
         <v>12.07</v>
       </c>
       <c r="O88" t="n">
+        <v>3.133333333333333</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1.566666666666667</v>
+      </c>
+      <c r="Q88" t="n">
         <v>25</v>
       </c>
-      <c r="P88" t="n">
+      <c r="R88" t="n">
         <v>1000</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="S88" t="n">
         <v>87.40000000000001</v>
       </c>
-      <c r="R88" t="n">
+      <c r="T88" t="n">
         <v>13.81915337493582</v>
-      </c>
-      <c r="S88" t="n">
-        <v>3.133333333333333</v>
-      </c>
-      <c r="T88" t="n">
-        <v>1.566666666666667</v>
       </c>
       <c r="U88" t="n">
         <v>-0.1473405878987091</v>
@@ -8980,22 +8980,22 @@
         <v>12.07</v>
       </c>
       <c r="O89" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P89" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q89" t="n">
         <v>39.2</v>
       </c>
-      <c r="P89" t="n">
+      <c r="R89" t="n">
         <v>4037.6</v>
       </c>
-      <c r="Q89" t="n">
+      <c r="S89" t="n">
         <v>66.92232018374371</v>
       </c>
-      <c r="R89" t="n">
+      <c r="T89" t="n">
         <v>6.594052143972789</v>
-      </c>
-      <c r="S89" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T89" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U89" t="n">
         <v>0.5777363290486176</v>
@@ -9075,22 +9075,22 @@
         <v>5.89</v>
       </c>
       <c r="O90" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="P90" t="n">
+        <v>1.633333333333333</v>
+      </c>
+      <c r="Q90" t="n">
         <v>32.3</v>
       </c>
-      <c r="P90" t="n">
+      <c r="R90" t="n">
         <v>1679.6</v>
       </c>
-      <c r="Q90" t="n">
+      <c r="S90" t="n">
         <v>83.57807199048719</v>
       </c>
-      <c r="R90" t="n">
+      <c r="T90" t="n">
         <v>11.59019323331239</v>
-      </c>
-      <c r="S90" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="T90" t="n">
-        <v>1.633333333333333</v>
       </c>
       <c r="U90" t="n">
         <v>0.2600539053343068</v>
@@ -9170,22 +9170,22 @@
         <v>6.29</v>
       </c>
       <c r="O91" t="n">
+        <v>2.533333333333333</v>
+      </c>
+      <c r="P91" t="n">
+        <v>1.266666666666667</v>
+      </c>
+      <c r="Q91" t="n">
         <v>25</v>
       </c>
-      <c r="P91" t="n">
+      <c r="R91" t="n">
         <v>1750</v>
       </c>
-      <c r="Q91" t="n">
+      <c r="S91" t="n">
         <v>95.2</v>
       </c>
-      <c r="R91" t="n">
+      <c r="T91" t="n">
         <v>11.37857636086343</v>
-      </c>
-      <c r="S91" t="n">
-        <v>2.533333333333333</v>
-      </c>
-      <c r="T91" t="n">
-        <v>1.266666666666667</v>
       </c>
       <c r="U91" t="n">
         <v>0.2941610385494901</v>
@@ -9265,22 +9265,22 @@
         <v>8.56</v>
       </c>
       <c r="O92" t="n">
+        <v>2.866666666666666</v>
+      </c>
+      <c r="P92" t="n">
+        <v>1.433333333333333</v>
+      </c>
+      <c r="Q92" t="n">
         <v>52.8</v>
       </c>
-      <c r="P92" t="n">
+      <c r="R92" t="n">
         <v>3590.4</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="S92" t="n">
         <v>43.90093013441363</v>
       </c>
-      <c r="R92" t="n">
+      <c r="T92" t="n">
         <v>5.323769764913198</v>
-      </c>
-      <c r="S92" t="n">
-        <v>2.866666666666666</v>
-      </c>
-      <c r="T92" t="n">
-        <v>1.433333333333333</v>
       </c>
       <c r="U92" t="n">
         <v>1.322289031143978</v>
@@ -9360,22 +9360,22 @@
         <v>2.66</v>
       </c>
       <c r="O93" t="n">
+        <v>4</v>
+      </c>
+      <c r="P93" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q93" t="n">
         <v>25.2</v>
       </c>
-      <c r="P93" t="n">
+      <c r="R93" t="n">
         <v>2293.2</v>
       </c>
-      <c r="Q93" t="n">
+      <c r="S93" t="n">
         <v>56.7733589433837</v>
       </c>
-      <c r="R93" t="n">
+      <c r="T93" t="n">
         <v>5.951465131011984</v>
-      </c>
-      <c r="S93" t="n">
-        <v>4</v>
-      </c>
-      <c r="T93" t="n">
-        <v>2</v>
       </c>
       <c r="U93" t="n">
         <v>0.8556911097452256</v>
@@ -9455,22 +9455,22 @@
         <v>13.45</v>
       </c>
       <c r="O94" t="n">
+        <v>3.133333333333333</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1.566666666666667</v>
+      </c>
+      <c r="Q94" t="n">
         <v>25</v>
       </c>
-      <c r="P94" t="n">
+      <c r="R94" t="n">
         <v>2425</v>
       </c>
-      <c r="Q94" t="n">
+      <c r="S94" t="n">
         <v>62.4</v>
       </c>
-      <c r="R94" t="n">
+      <c r="T94" t="n">
         <v>6.335760070433783</v>
-      </c>
-      <c r="S94" t="n">
-        <v>3.133333333333333</v>
-      </c>
-      <c r="T94" t="n">
-        <v>1.566666666666667</v>
       </c>
       <c r="U94" t="n">
         <v>0.2398039922073169</v>
@@ -9550,22 +9550,22 @@
         <v>6.14</v>
       </c>
       <c r="O95" t="n">
+        <v>3.133333333333333</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1.566666666666667</v>
+      </c>
+      <c r="Q95" t="n">
         <v>56</v>
       </c>
-      <c r="P95" t="n">
+      <c r="R95" t="n">
         <v>6384</v>
       </c>
-      <c r="Q95" t="n">
+      <c r="S95" t="n">
         <v>63.47454495420079</v>
       </c>
-      <c r="R95" t="n">
+      <c r="T95" t="n">
         <v>5.944935820070887</v>
-      </c>
-      <c r="S95" t="n">
-        <v>3.133333333333333</v>
-      </c>
-      <c r="T95" t="n">
-        <v>1.566666666666667</v>
       </c>
       <c r="U95" t="n">
         <v>0.6318035503188933</v>
@@ -9645,22 +9645,22 @@
         <v>30.41</v>
       </c>
       <c r="O96" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q96" t="n">
         <v>34.3</v>
       </c>
-      <c r="P96" t="n">
+      <c r="R96" t="n">
         <v>2572.5</v>
       </c>
-      <c r="Q96" t="n">
+      <c r="S96" t="n">
         <v>84.00749654178881</v>
       </c>
-      <c r="R96" t="n">
+      <c r="T96" t="n">
         <v>9.700350148469665</v>
-      </c>
-      <c r="S96" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T96" t="n">
-        <v>1.4</v>
       </c>
       <c r="U96" t="n">
         <v>0.554459660786052</v>
@@ -9740,22 +9740,22 @@
         <v>3.48</v>
       </c>
       <c r="O97" t="n">
+        <v>3.866666666666666</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1.933333333333333</v>
+      </c>
+      <c r="Q97" t="n">
         <v>38.9</v>
       </c>
-      <c r="P97" t="n">
+      <c r="R97" t="n">
         <v>4240.099999999999</v>
       </c>
-      <c r="Q97" t="n">
+      <c r="S97" t="n">
         <v>55.79617699815334</v>
       </c>
-      <c r="R97" t="n">
+      <c r="T97" t="n">
         <v>5.344304494368306</v>
-      </c>
-      <c r="S97" t="n">
-        <v>3.866666666666666</v>
-      </c>
-      <c r="T97" t="n">
-        <v>1.933333333333333</v>
       </c>
       <c r="U97" t="n">
         <v>0.9547419182484077</v>
@@ -9770,7 +9770,7 @@
         <v>5.852202479774474</v>
       </c>
       <c r="Y97" t="n">
-        <v>3.6609942506244</v>
+        <v>3.660994250624401</v>
       </c>
       <c r="Z97" t="n">
         <v>8.352342132853545</v>
@@ -9835,22 +9835,22 @@
         <v>3.02</v>
       </c>
       <c r="O98" t="n">
+        <v>3.866666666666666</v>
+      </c>
+      <c r="P98" t="n">
+        <v>1.933333333333333</v>
+      </c>
+      <c r="Q98" t="n">
         <v>36.8</v>
       </c>
-      <c r="P98" t="n">
+      <c r="R98" t="n">
         <v>3459.2</v>
       </c>
-      <c r="Q98" t="n">
+      <c r="S98" t="n">
         <v>45.8269429010072</v>
       </c>
-      <c r="R98" t="n">
+      <c r="T98" t="n">
         <v>4.726688255918741</v>
-      </c>
-      <c r="S98" t="n">
-        <v>3.866666666666666</v>
-      </c>
-      <c r="T98" t="n">
-        <v>1.933333333333333</v>
       </c>
       <c r="U98" t="n">
         <v>1.227298629629433</v>
@@ -9930,25 +9930,25 @@
         <v>4.34</v>
       </c>
       <c r="O99" t="n">
+        <v>2.933333333333334</v>
+      </c>
+      <c r="P99" t="n">
+        <v>1.466666666666667</v>
+      </c>
+      <c r="Q99" t="n">
         <v>25</v>
       </c>
-      <c r="P99" t="n">
+      <c r="R99" t="n">
         <v>4325</v>
       </c>
-      <c r="Q99" t="n">
+      <c r="S99" t="n">
         <v>76</v>
       </c>
-      <c r="R99" t="n">
+      <c r="T99" t="n">
         <v>5.778173001649762</v>
       </c>
-      <c r="S99" t="n">
-        <v>2.933333333333334</v>
-      </c>
-      <c r="T99" t="n">
-        <v>1.466666666666667</v>
-      </c>
       <c r="U99" t="n">
-        <v>0.6549259677397476</v>
+        <v>0.6549259677397475</v>
       </c>
       <c r="V99" t="n">
         <v>4.330733340286331</v>
@@ -10025,25 +10025,25 @@
         <v>4.15</v>
       </c>
       <c r="O100" t="n">
+        <v>4.133333333333333</v>
+      </c>
+      <c r="P100" t="n">
+        <v>2.066666666666666</v>
+      </c>
+      <c r="Q100" t="n">
         <v>41.3</v>
       </c>
-      <c r="P100" t="n">
+      <c r="R100" t="n">
         <v>3469.2</v>
       </c>
-      <c r="Q100" t="n">
+      <c r="S100" t="n">
         <v>61.15296583179113</v>
       </c>
-      <c r="R100" t="n">
+      <c r="T100" t="n">
         <v>6.672335592743595</v>
       </c>
-      <c r="S100" t="n">
-        <v>4.133333333333333</v>
-      </c>
-      <c r="T100" t="n">
-        <v>2.066666666666666</v>
-      </c>
       <c r="U100" t="n">
-        <v>0.7691818668359428</v>
+        <v>0.7691818668359429</v>
       </c>
       <c r="V100" t="n">
         <v>4.113378361885768</v>
@@ -10120,22 +10120,22 @@
         <v>7.12</v>
       </c>
       <c r="O101" t="n">
+        <v>3.133333333333333</v>
+      </c>
+      <c r="P101" t="n">
+        <v>1.566666666666667</v>
+      </c>
+      <c r="Q101" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="P101" t="n">
+      <c r="R101" t="n">
         <v>8532</v>
       </c>
-      <c r="Q101" t="n">
+      <c r="S101" t="n">
         <v>43.76143611833643</v>
       </c>
-      <c r="R101" t="n">
+      <c r="T101" t="n">
         <v>3.99485428513903</v>
-      </c>
-      <c r="S101" t="n">
-        <v>3.133333333333333</v>
-      </c>
-      <c r="T101" t="n">
-        <v>1.566666666666667</v>
       </c>
       <c r="U101" t="n">
         <v>0.6734545472142093</v>
@@ -10147,7 +10147,7 @@
         <v>1.385007104244907</v>
       </c>
       <c r="X101" t="n">
-        <v>5.910796644040527</v>
+        <v>5.910796644040528</v>
       </c>
       <c r="Y101" t="n">
         <v>4.264087336809195</v>
@@ -10215,22 +10215,22 @@
         <v>12.99</v>
       </c>
       <c r="O102" t="n">
+        <v>3.866666666666666</v>
+      </c>
+      <c r="P102" t="n">
+        <v>1.933333333333333</v>
+      </c>
+      <c r="Q102" t="n">
         <v>44.9</v>
       </c>
-      <c r="P102" t="n">
+      <c r="R102" t="n">
         <v>3681.8</v>
       </c>
-      <c r="Q102" t="n">
+      <c r="S102" t="n">
         <v>74.46931775775258</v>
       </c>
-      <c r="R102" t="n">
+      <c r="T102" t="n">
         <v>8.223760405741286</v>
-      </c>
-      <c r="S102" t="n">
-        <v>3.866666666666666</v>
-      </c>
-      <c r="T102" t="n">
-        <v>1.933333333333333</v>
       </c>
       <c r="U102" t="n">
         <v>0.5007752879124892</v>
@@ -10310,22 +10310,22 @@
         <v>4.33</v>
       </c>
       <c r="O103" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="P103" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="Q103" t="n">
         <v>33.8</v>
       </c>
-      <c r="P103" t="n">
+      <c r="R103" t="n">
         <v>3785.599999999999</v>
       </c>
-      <c r="Q103" t="n">
+      <c r="S103" t="n">
         <v>57.10573604076387</v>
       </c>
-      <c r="R103" t="n">
+      <c r="T103" t="n">
         <v>5.395984857112837</v>
-      </c>
-      <c r="S103" t="n">
-        <v>4.666666666666666</v>
-      </c>
-      <c r="T103" t="n">
-        <v>2.333333333333333</v>
       </c>
       <c r="U103" t="n">
         <v>0.6554453133759338</v>
@@ -10405,22 +10405,22 @@
         <v>6.71</v>
       </c>
       <c r="O104" t="n">
+        <v>4</v>
+      </c>
+      <c r="P104" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q104" t="n">
         <v>47.2</v>
       </c>
-      <c r="P104" t="n">
+      <c r="R104" t="n">
         <v>4767.200000000001</v>
       </c>
-      <c r="Q104" t="n">
+      <c r="S104" t="n">
         <v>49.78002458273426</v>
       </c>
-      <c r="R104" t="n">
+      <c r="T104" t="n">
         <v>4.953297578938808</v>
-      </c>
-      <c r="S104" t="n">
-        <v>4</v>
-      </c>
-      <c r="T104" t="n">
-        <v>2</v>
       </c>
       <c r="U104" t="n">
         <v>1.151837049905408</v>
@@ -10432,7 +10432,7 @@
         <v>1.600053532346221</v>
       </c>
       <c r="X104" t="n">
-        <v>5.834810737062605</v>
+        <v>5.834810737062606</v>
       </c>
       <c r="Y104" t="n">
         <v>3.85439389259151</v>
@@ -10500,22 +10500,22 @@
         <v>10.14</v>
       </c>
       <c r="O105" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P105" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q105" t="n">
         <v>60.3</v>
       </c>
-      <c r="P105" t="n">
+      <c r="R105" t="n">
         <v>6271.2</v>
       </c>
-      <c r="Q105" t="n">
+      <c r="S105" t="n">
         <v>57.30616618873064</v>
       </c>
-      <c r="R105" t="n">
+      <c r="T105" t="n">
         <v>5.619331916260165</v>
-      </c>
-      <c r="S105" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T105" t="n">
-        <v>2.3</v>
       </c>
       <c r="U105" t="n">
         <v>0.9485642924244507</v>
@@ -10595,22 +10595,22 @@
         <v>9.369999999999999</v>
       </c>
       <c r="O106" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P106" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q106" t="n">
         <v>42.7</v>
       </c>
-      <c r="P106" t="n">
+      <c r="R106" t="n">
         <v>7686.000000000001</v>
       </c>
-      <c r="Q106" t="n">
+      <c r="S106" t="n">
         <v>73.91510415977793</v>
       </c>
-      <c r="R106" t="n">
+      <c r="T106" t="n">
         <v>5.509306582174696</v>
-      </c>
-      <c r="S106" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T106" t="n">
-        <v>1.6</v>
       </c>
       <c r="U106" t="n">
         <v>0.332894415273329</v>
@@ -10690,22 +10690,22 @@
         <v>15.49</v>
       </c>
       <c r="O107" t="n">
+        <v>3.066666666666666</v>
+      </c>
+      <c r="P107" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="Q107" t="n">
         <v>32.6</v>
       </c>
-      <c r="P107" t="n">
+      <c r="R107" t="n">
         <v>3390.4</v>
       </c>
-      <c r="Q107" t="n">
+      <c r="S107" t="n">
         <v>50.26585761446621</v>
       </c>
-      <c r="R107" t="n">
+      <c r="T107" t="n">
         <v>4.928972862377687</v>
-      </c>
-      <c r="S107" t="n">
-        <v>3.066666666666666</v>
-      </c>
-      <c r="T107" t="n">
-        <v>1.533333333333333</v>
       </c>
       <c r="U107" t="n">
         <v>1.216691576733711</v>
@@ -10785,22 +10785,22 @@
         <v>2.77</v>
       </c>
       <c r="O108" t="n">
+        <v>4.066666666666666</v>
+      </c>
+      <c r="P108" t="n">
+        <v>2.033333333333333</v>
+      </c>
+      <c r="Q108" t="n">
         <v>26.3</v>
       </c>
-      <c r="P108" t="n">
+      <c r="R108" t="n">
         <v>2577.4</v>
       </c>
-      <c r="Q108" t="n">
+      <c r="S108" t="n">
         <v>98.08218017785426</v>
       </c>
-      <c r="R108" t="n">
+      <c r="T108" t="n">
         <v>9.907796388188787</v>
-      </c>
-      <c r="S108" t="n">
-        <v>4.066666666666666</v>
-      </c>
-      <c r="T108" t="n">
-        <v>2.033333333333333</v>
       </c>
       <c r="U108" t="n">
         <v>0.01192857086527381</v>
@@ -10880,22 +10880,22 @@
         <v>9.02</v>
       </c>
       <c r="O109" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="P109" t="n">
+        <v>1.633333333333333</v>
+      </c>
+      <c r="Q109" t="n">
         <v>35.9</v>
       </c>
-      <c r="P109" t="n">
+      <c r="R109" t="n">
         <v>1436</v>
       </c>
-      <c r="Q109" t="n">
+      <c r="S109" t="n">
         <v>56.41173745385506</v>
       </c>
-      <c r="R109" t="n">
+      <c r="T109" t="n">
         <v>8.919478856080486</v>
-      </c>
-      <c r="S109" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="T109" t="n">
-        <v>1.633333333333333</v>
       </c>
       <c r="U109" t="n">
         <v>0.9182887345368281</v>
@@ -10975,25 +10975,25 @@
         <v>6.29</v>
       </c>
       <c r="O110" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P110" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q110" t="n">
         <v>78.59999999999999</v>
       </c>
-      <c r="P110" t="n">
+      <c r="R110" t="n">
         <v>7231.2</v>
       </c>
-      <c r="Q110" t="n">
+      <c r="S110" t="n">
         <v>47.03539352737265</v>
       </c>
-      <c r="R110" t="n">
+      <c r="T110" t="n">
         <v>4.903778760652018</v>
       </c>
-      <c r="S110" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T110" t="n">
-        <v>1.666666666666667</v>
-      </c>
       <c r="U110" t="n">
-        <v>0.9481769207364769</v>
+        <v>0.9481769207364767</v>
       </c>
       <c r="V110" t="n">
         <v>3.850900372081221</v>
@@ -11070,22 +11070,22 @@
         <v>25.87</v>
       </c>
       <c r="O111" t="n">
+        <v>4.333333333333333</v>
+      </c>
+      <c r="P111" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="Q111" t="n">
         <v>41.6</v>
       </c>
-      <c r="P111" t="n">
+      <c r="R111" t="n">
         <v>3369.6</v>
       </c>
-      <c r="Q111" t="n">
+      <c r="S111" t="n">
         <v>50.23406750862942</v>
       </c>
-      <c r="R111" t="n">
+      <c r="T111" t="n">
         <v>5.581563056514381</v>
-      </c>
-      <c r="S111" t="n">
-        <v>4.333333333333333</v>
-      </c>
-      <c r="T111" t="n">
-        <v>2.166666666666667</v>
       </c>
       <c r="U111" t="n">
         <v>1.029619417181158</v>
@@ -11100,7 +11100,7 @@
         <v>5.780743515792329</v>
       </c>
       <c r="Y111" t="n">
-        <v>3.728100167267218</v>
+        <v>3.728100167267217</v>
       </c>
       <c r="Z111" t="n">
         <v>8.122549321939655</v>
@@ -11165,22 +11165,22 @@
         <v>4.84</v>
       </c>
       <c r="O112" t="n">
+        <v>3.066666666666666</v>
+      </c>
+      <c r="P112" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="Q112" t="n">
         <v>52.5</v>
       </c>
-      <c r="P112" t="n">
+      <c r="R112" t="n">
         <v>2257.5</v>
       </c>
-      <c r="Q112" t="n">
+      <c r="S112" t="n">
         <v>49.68472027264951</v>
       </c>
-      <c r="R112" t="n">
+      <c r="T112" t="n">
         <v>7.57684880895443</v>
-      </c>
-      <c r="S112" t="n">
-        <v>3.066666666666666</v>
-      </c>
-      <c r="T112" t="n">
-        <v>1.533333333333333</v>
       </c>
       <c r="U112" t="n">
         <v>1.024965748499811</v>
@@ -11260,22 +11260,22 @@
         <v>11.32</v>
       </c>
       <c r="O113" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P113" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q113" t="n">
         <v>38</v>
       </c>
-      <c r="P113" t="n">
+      <c r="R113" t="n">
         <v>4066</v>
       </c>
-      <c r="Q113" t="n">
+      <c r="S113" t="n">
         <v>80.1373820385967</v>
       </c>
-      <c r="R113" t="n">
+      <c r="T113" t="n">
         <v>7.747173135330399</v>
-      </c>
-      <c r="S113" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T113" t="n">
-        <v>1.3</v>
       </c>
       <c r="U113" t="n">
         <v>0.4173936789734382</v>
@@ -11287,7 +11287,7 @@
         <v>2.047328020093777</v>
       </c>
       <c r="X113" t="n">
-        <v>6.202535517187923</v>
+        <v>6.202535517187922</v>
       </c>
       <c r="Y113" t="n">
         <v>3.637586159726386</v>
@@ -11355,22 +11355,22 @@
         <v>6.88</v>
       </c>
       <c r="O114" t="n">
+        <v>3.466666666666667</v>
+      </c>
+      <c r="P114" t="n">
+        <v>1.733333333333333</v>
+      </c>
+      <c r="Q114" t="n">
         <v>25</v>
       </c>
-      <c r="P114" t="n">
+      <c r="R114" t="n">
         <v>1450</v>
       </c>
-      <c r="Q114" t="n">
+      <c r="S114" t="n">
         <v>94.40000000000001</v>
       </c>
-      <c r="R114" t="n">
+      <c r="T114" t="n">
         <v>12.39532726195781</v>
-      </c>
-      <c r="S114" t="n">
-        <v>3.466666666666667</v>
-      </c>
-      <c r="T114" t="n">
-        <v>1.733333333333333</v>
       </c>
       <c r="U114" t="n">
         <v>0.1501426584297194</v>
@@ -11450,22 +11450,22 @@
         <v>5.29</v>
       </c>
       <c r="O115" t="n">
+        <v>3</v>
+      </c>
+      <c r="P115" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q115" t="n">
         <v>51.2</v>
       </c>
-      <c r="P115" t="n">
+      <c r="R115" t="n">
         <v>6400</v>
       </c>
-      <c r="Q115" t="n">
+      <c r="S115" t="n">
         <v>75.04803149483669</v>
       </c>
-      <c r="R115" t="n">
+      <c r="T115" t="n">
         <v>6.7125</v>
-      </c>
-      <c r="S115" t="n">
-        <v>3</v>
-      </c>
-      <c r="T115" t="n">
-        <v>1.5</v>
       </c>
       <c r="U115" t="n">
         <v>0.3045391895182039</v>
@@ -11545,22 +11545,22 @@
         <v>6.62</v>
       </c>
       <c r="O116" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P116" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q116" t="n">
         <v>42.5</v>
       </c>
-      <c r="P116" t="n">
+      <c r="R116" t="n">
         <v>2337.5</v>
       </c>
-      <c r="Q116" t="n">
+      <c r="S116" t="n">
         <v>47.39843631076749</v>
       </c>
-      <c r="R116" t="n">
+      <c r="T116" t="n">
         <v>6.391203848338437</v>
-      </c>
-      <c r="S116" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T116" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U116" t="n">
         <v>1.104594360345657</v>
@@ -11572,7 +11572,7 @@
         <v>1.854922646316324</v>
       </c>
       <c r="X116" t="n">
-        <v>5.733341276897746</v>
+        <v>5.733341276897745</v>
       </c>
       <c r="Y116" t="n">
         <v>3.749504075930371</v>
@@ -11640,22 +11640,22 @@
         <v>8</v>
       </c>
       <c r="O117" t="n">
+        <v>3.533333333333333</v>
+      </c>
+      <c r="P117" t="n">
+        <v>1.766666666666667</v>
+      </c>
+      <c r="Q117" t="n">
         <v>37.2</v>
       </c>
-      <c r="P117" t="n">
+      <c r="R117" t="n">
         <v>3348</v>
       </c>
-      <c r="Q117" t="n">
+      <c r="S117" t="n">
         <v>46.39967788171467</v>
       </c>
-      <c r="R117" t="n">
+      <c r="T117" t="n">
         <v>4.890955493478505</v>
-      </c>
-      <c r="S117" t="n">
-        <v>3.533333333333333</v>
-      </c>
-      <c r="T117" t="n">
-        <v>1.766666666666667</v>
       </c>
       <c r="U117" t="n">
         <v>1.198457623637826</v>
@@ -11735,22 +11735,22 @@
         <v>27.98</v>
       </c>
       <c r="O118" t="n">
+        <v>4.466666666666667</v>
+      </c>
+      <c r="P118" t="n">
+        <v>2.233333333333333</v>
+      </c>
+      <c r="Q118" t="n">
         <v>43.8</v>
       </c>
-      <c r="P118" t="n">
+      <c r="R118" t="n">
         <v>5431.2</v>
       </c>
-      <c r="Q118" t="n">
+      <c r="S118" t="n">
         <v>47.59633346072058</v>
       </c>
-      <c r="R118" t="n">
+      <c r="T118" t="n">
         <v>4.274276923289906</v>
-      </c>
-      <c r="S118" t="n">
-        <v>4.466666666666667</v>
-      </c>
-      <c r="T118" t="n">
-        <v>2.233333333333333</v>
       </c>
       <c r="U118" t="n">
         <v>1.103599830179149</v>
@@ -11830,25 +11830,25 @@
         <v>5.02</v>
       </c>
       <c r="O119" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P119" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q119" t="n">
         <v>28.7</v>
       </c>
-      <c r="P119" t="n">
+      <c r="R119" t="n">
         <v>1951.6</v>
       </c>
-      <c r="Q119" t="n">
+      <c r="S119" t="n">
         <v>89.97173385006018</v>
       </c>
-      <c r="R119" t="n">
+      <c r="T119" t="n">
         <v>10.91067535246347</v>
       </c>
-      <c r="S119" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T119" t="n">
-        <v>1.2</v>
-      </c>
       <c r="U119" t="n">
-        <v>-0.20089294237939</v>
+        <v>-0.2008929423793901</v>
       </c>
       <c r="V119" t="n">
         <v>4.499495552667812</v>
@@ -11925,22 +11925,22 @@
         <v>5.97</v>
       </c>
       <c r="O120" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P120" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q120" t="n">
         <v>49.1</v>
       </c>
-      <c r="P120" t="n">
+      <c r="R120" t="n">
         <v>1964</v>
       </c>
-      <c r="Q120" t="n">
+      <c r="S120" t="n">
         <v>74.06731676955738</v>
       </c>
-      <c r="R120" t="n">
+      <c r="T120" t="n">
         <v>11.7110710584493</v>
-      </c>
-      <c r="S120" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T120" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U120" t="n">
         <v>0.7547125362181001</v>
@@ -12020,22 +12020,22 @@
         <v>15.68</v>
       </c>
       <c r="O121" t="n">
+        <v>3.066666666666666</v>
+      </c>
+      <c r="P121" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="Q121" t="n">
         <v>39.3</v>
       </c>
-      <c r="P121" t="n">
+      <c r="R121" t="n">
         <v>1572</v>
       </c>
-      <c r="Q121" t="n">
+      <c r="S121" t="n">
         <v>77.52468210755761</v>
       </c>
-      <c r="R121" t="n">
+      <c r="T121" t="n">
         <v>12.25772851701923</v>
-      </c>
-      <c r="S121" t="n">
-        <v>3.066666666666666</v>
-      </c>
-      <c r="T121" t="n">
-        <v>1.533333333333333</v>
       </c>
       <c r="U121" t="n">
         <v>0.05354076692802976</v>
@@ -12047,7 +12047,7 @@
         <v>2.506156637405918</v>
       </c>
       <c r="X121" t="n">
-        <v>6.186208623900494</v>
+        <v>6.186208623900495</v>
       </c>
       <c r="Y121" t="n">
         <v>3.671224518875215</v>
@@ -12115,22 +12115,22 @@
         <v>7.88</v>
       </c>
       <c r="O122" t="n">
+        <v>4.066666666666666</v>
+      </c>
+      <c r="P122" t="n">
+        <v>2.033333333333333</v>
+      </c>
+      <c r="Q122" t="n">
         <v>25</v>
       </c>
-      <c r="P122" t="n">
+      <c r="R122" t="n">
         <v>2050</v>
       </c>
-      <c r="Q122" t="n">
+      <c r="S122" t="n">
         <v>97.2</v>
       </c>
-      <c r="R122" t="n">
+      <c r="T122" t="n">
         <v>10.73394433447508</v>
-      </c>
-      <c r="S122" t="n">
-        <v>4.066666666666666</v>
-      </c>
-      <c r="T122" t="n">
-        <v>2.033333333333333</v>
       </c>
       <c r="U122" t="n">
         <v>0.01783991812833102</v>
@@ -12142,7 +12142,7 @@
         <v>2.373411087834267</v>
       </c>
       <c r="X122" t="n">
-        <v>6.186208623900494</v>
+        <v>6.186208623900495</v>
       </c>
       <c r="Y122" t="n">
         <v>3.218875824868201</v>
@@ -12210,22 +12210,22 @@
         <v>25.6</v>
       </c>
       <c r="O123" t="n">
+        <v>3.399999999999999</v>
+      </c>
+      <c r="P123" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q123" t="n">
         <v>41.8</v>
       </c>
-      <c r="P123" t="n">
+      <c r="R123" t="n">
         <v>3302.2</v>
       </c>
-      <c r="Q123" t="n">
+      <c r="S123" t="n">
         <v>71.45848997476566</v>
       </c>
-      <c r="R123" t="n">
+      <c r="T123" t="n">
         <v>8.039708248905242</v>
-      </c>
-      <c r="S123" t="n">
-        <v>3.399999999999999</v>
-      </c>
-      <c r="T123" t="n">
-        <v>1.7</v>
       </c>
       <c r="U123" t="n">
         <v>0.3886579897917832</v>
@@ -12237,7 +12237,7 @@
         <v>2.084392795082873</v>
       </c>
       <c r="X123" t="n">
-        <v>6.135564891081739</v>
+        <v>6.13556489108174</v>
       </c>
       <c r="Y123" t="n">
         <v>3.73289633953071</v>
@@ -12305,22 +12305,22 @@
         <v>5.82</v>
       </c>
       <c r="O124" t="n">
+        <v>4.199999999999999</v>
+      </c>
+      <c r="P124" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q124" t="n">
         <v>60.3</v>
       </c>
-      <c r="P124" t="n">
+      <c r="R124" t="n">
         <v>2412</v>
       </c>
-      <c r="Q124" t="n">
+      <c r="S124" t="n">
         <v>32.06569748537962</v>
       </c>
-      <c r="R124" t="n">
+      <c r="T124" t="n">
         <v>5.070031940786667</v>
-      </c>
-      <c r="S124" t="n">
-        <v>4.199999999999999</v>
-      </c>
-      <c r="T124" t="n">
-        <v>2.1</v>
       </c>
       <c r="U124" t="n">
         <v>1.85410809429259</v>
@@ -12332,7 +12332,7 @@
         <v>1.62334711754117</v>
       </c>
       <c r="X124" t="n">
-        <v>5.517452896464707</v>
+        <v>5.517452896464708</v>
       </c>
       <c r="Y124" t="n">
         <v>4.09933210373314</v>
@@ -12400,22 +12400,22 @@
         <v>35</v>
       </c>
       <c r="O125" t="n">
+        <v>4.266666666666667</v>
+      </c>
+      <c r="P125" t="n">
+        <v>2.133333333333333</v>
+      </c>
+      <c r="Q125" t="n">
         <v>25</v>
       </c>
-      <c r="P125" t="n">
+      <c r="R125" t="n">
         <v>2400</v>
       </c>
-      <c r="Q125" t="n">
+      <c r="S125" t="n">
         <v>104.2</v>
       </c>
-      <c r="R125" t="n">
+      <c r="T125" t="n">
         <v>10.63486796658363</v>
-      </c>
-      <c r="S125" t="n">
-        <v>4.266666666666667</v>
-      </c>
-      <c r="T125" t="n">
-        <v>2.133333333333333</v>
       </c>
       <c r="U125" t="n">
         <v>-0.06400532997591243</v>
@@ -12495,22 +12495,22 @@
         <v>3.27</v>
       </c>
       <c r="O126" t="n">
+        <v>3</v>
+      </c>
+      <c r="P126" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q126" t="n">
         <v>41.2</v>
       </c>
-      <c r="P126" t="n">
+      <c r="R126" t="n">
         <v>5232.400000000001</v>
       </c>
-      <c r="Q126" t="n">
+      <c r="S126" t="n">
         <v>61.85031257033827</v>
       </c>
-      <c r="R126" t="n">
+      <c r="T126" t="n">
         <v>5.488327746871094</v>
-      </c>
-      <c r="S126" t="n">
-        <v>3</v>
-      </c>
-      <c r="T126" t="n">
-        <v>1.5</v>
       </c>
       <c r="U126" t="n">
         <v>0.9738046380747618</v>
@@ -12590,22 +12590,22 @@
         <v>6.38</v>
       </c>
       <c r="O127" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="P127" t="n">
+        <v>1.633333333333333</v>
+      </c>
+      <c r="Q127" t="n">
         <v>42.5</v>
       </c>
-      <c r="P127" t="n">
+      <c r="R127" t="n">
         <v>3782.5</v>
       </c>
-      <c r="Q127" t="n">
+      <c r="S127" t="n">
         <v>44.02379035983906</v>
       </c>
-      <c r="R127" t="n">
+      <c r="T127" t="n">
         <v>4.666512445127383</v>
-      </c>
-      <c r="S127" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="T127" t="n">
-        <v>1.633333333333333</v>
       </c>
       <c r="U127" t="n">
         <v>1.288405860300765</v>
@@ -12685,22 +12685,22 @@
         <v>35</v>
       </c>
       <c r="O128" t="n">
+        <v>3.533333333333333</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1.766666666666667</v>
+      </c>
+      <c r="Q128" t="n">
         <v>30.3</v>
       </c>
-      <c r="P128" t="n">
+      <c r="R128" t="n">
         <v>3575.4</v>
       </c>
-      <c r="Q128" t="n">
+      <c r="S128" t="n">
         <v>93.3774059073896</v>
       </c>
-      <c r="R128" t="n">
+      <c r="T128" t="n">
         <v>8.596086976353183</v>
-      </c>
-      <c r="S128" t="n">
-        <v>3.533333333333333</v>
-      </c>
-      <c r="T128" t="n">
-        <v>1.766666666666667</v>
       </c>
       <c r="U128" t="n">
         <v>0.3126185577418125</v>
@@ -12780,25 +12780,25 @@
         <v>23.52</v>
       </c>
       <c r="O129" t="n">
+        <v>3</v>
+      </c>
+      <c r="P129" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q129" t="n">
         <v>35</v>
       </c>
-      <c r="P129" t="n">
+      <c r="R129" t="n">
         <v>3885</v>
       </c>
-      <c r="Q129" t="n">
+      <c r="S129" t="n">
         <v>79.78256164637196</v>
       </c>
-      <c r="R129" t="n">
+      <c r="T129" t="n">
         <v>7.572625630827061</v>
       </c>
-      <c r="S129" t="n">
-        <v>3</v>
-      </c>
-      <c r="T129" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U129" t="n">
-        <v>0.4337285733810238</v>
+        <v>0.4337285733810237</v>
       </c>
       <c r="V129" t="n">
         <v>4.379304954840848</v>
@@ -12875,25 +12875,25 @@
         <v>9.44</v>
       </c>
       <c r="O130" t="n">
+        <v>2.133333333333333</v>
+      </c>
+      <c r="P130" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="Q130" t="n">
         <v>25</v>
       </c>
-      <c r="P130" t="n">
+      <c r="R130" t="n">
         <v>2400</v>
       </c>
-      <c r="Q130" t="n">
+      <c r="S130" t="n">
         <v>74</v>
       </c>
-      <c r="R130" t="n">
+      <c r="T130" t="n">
         <v>7.552593373581466</v>
       </c>
-      <c r="S130" t="n">
-        <v>2.133333333333333</v>
-      </c>
-      <c r="T130" t="n">
-        <v>1.066666666666667</v>
-      </c>
       <c r="U130" t="n">
-        <v>-0.06720874969345</v>
+        <v>-0.06720874969344999</v>
       </c>
       <c r="V130" t="n">
         <v>4.30406509320417</v>
@@ -12902,7 +12902,7 @@
         <v>2.021890997470252</v>
       </c>
       <c r="X130" t="n">
-        <v>5.91350300563827</v>
+        <v>5.913503005638271</v>
       </c>
       <c r="Y130" t="n">
         <v>3.218875824868201</v>
@@ -12970,22 +12970,22 @@
         <v>2.9</v>
       </c>
       <c r="O131" t="n">
+        <v>2.133333333333333</v>
+      </c>
+      <c r="P131" t="n">
+        <v>1.066666666666667</v>
+      </c>
+      <c r="Q131" t="n">
         <v>26.8</v>
       </c>
-      <c r="P131" t="n">
+      <c r="R131" t="n">
         <v>2224.4</v>
       </c>
-      <c r="Q131" t="n">
+      <c r="S131" t="n">
         <v>67.22206460790426</v>
       </c>
-      <c r="R131" t="n">
+      <c r="T131" t="n">
         <v>7.378580176665764</v>
-      </c>
-      <c r="S131" t="n">
-        <v>2.133333333333333</v>
-      </c>
-      <c r="T131" t="n">
-        <v>1.066666666666667</v>
       </c>
       <c r="U131" t="n">
         <v>0.7462139014966376</v>
@@ -13065,22 +13065,22 @@
         <v>18.49</v>
       </c>
       <c r="O132" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P132" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q132" t="n">
         <v>32.2</v>
       </c>
-      <c r="P132" t="n">
+      <c r="R132" t="n">
         <v>3123.4</v>
       </c>
-      <c r="Q132" t="n">
+      <c r="S132" t="n">
         <v>67.31865448919805</v>
       </c>
-      <c r="R132" t="n">
+      <c r="T132" t="n">
         <v>6.835173767756232</v>
-      </c>
-      <c r="S132" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T132" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U132" t="n">
         <v>0.6259384308664954</v>
@@ -13160,22 +13160,22 @@
         <v>4.18</v>
       </c>
       <c r="O133" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q133" t="n">
         <v>44.6</v>
       </c>
-      <c r="P133" t="n">
+      <c r="R133" t="n">
         <v>5441.2</v>
       </c>
-      <c r="Q133" t="n">
+      <c r="S133" t="n">
         <v>78.76228639296559</v>
       </c>
-      <c r="R133" t="n">
+      <c r="T133" t="n">
         <v>7.130802358601645</v>
-      </c>
-      <c r="S133" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T133" t="n">
-        <v>1.8</v>
       </c>
       <c r="U133" t="n">
         <v>0.554459660786052</v>
@@ -13190,7 +13190,7 @@
         <v>6.26530121273771</v>
       </c>
       <c r="Y133" t="n">
-        <v>3.797733859026018</v>
+        <v>3.797733859026019</v>
       </c>
       <c r="Z133" t="n">
         <v>8.601754903759275</v>
@@ -13255,22 +13255,22 @@
         <v>10.18</v>
       </c>
       <c r="O134" t="n">
+        <v>2.866666666666666</v>
+      </c>
+      <c r="P134" t="n">
+        <v>1.433333333333333</v>
+      </c>
+      <c r="Q134" t="n">
         <v>34.4</v>
       </c>
-      <c r="P134" t="n">
+      <c r="R134" t="n">
         <v>2064</v>
       </c>
-      <c r="Q134" t="n">
+      <c r="S134" t="n">
         <v>79.45234054831016</v>
       </c>
-      <c r="R134" t="n">
+      <c r="T134" t="n">
         <v>10.25725305869352</v>
-      </c>
-      <c r="S134" t="n">
-        <v>2.866666666666666</v>
-      </c>
-      <c r="T134" t="n">
-        <v>1.433333333333333</v>
       </c>
       <c r="U134" t="n">
         <v>0.1561486824899314</v>
@@ -13350,22 +13350,22 @@
         <v>11.82</v>
       </c>
       <c r="O135" t="n">
+        <v>3.466666666666667</v>
+      </c>
+      <c r="P135" t="n">
+        <v>1.733333333333333</v>
+      </c>
+      <c r="Q135" t="n">
         <v>42.3</v>
       </c>
-      <c r="P135" t="n">
+      <c r="R135" t="n">
         <v>3468.6</v>
       </c>
-      <c r="Q135" t="n">
+      <c r="S135" t="n">
         <v>73.80249664231081</v>
       </c>
-      <c r="R135" t="n">
+      <c r="T135" t="n">
         <v>8.15012233234412</v>
-      </c>
-      <c r="S135" t="n">
-        <v>3.466666666666667</v>
-      </c>
-      <c r="T135" t="n">
-        <v>1.733333333333333</v>
       </c>
       <c r="U135" t="n">
         <v>0.3191807395111518</v>
@@ -13380,7 +13380,7 @@
         <v>6.173786103901937</v>
       </c>
       <c r="Y135" t="n">
-        <v>3.744787086052232</v>
+        <v>3.744787086052233</v>
       </c>
       <c r="Z135" t="n">
         <v>8.151506333316487</v>
@@ -13445,22 +13445,22 @@
         <v>16.29</v>
       </c>
       <c r="O136" t="n">
+        <v>2.866666666666666</v>
+      </c>
+      <c r="P136" t="n">
+        <v>1.433333333333333</v>
+      </c>
+      <c r="Q136" t="n">
         <v>51.3</v>
       </c>
-      <c r="P136" t="n">
+      <c r="R136" t="n">
         <v>6361.2</v>
       </c>
-      <c r="Q136" t="n">
+      <c r="S136" t="n">
         <v>50.68132290329515</v>
       </c>
-      <c r="R136" t="n">
+      <c r="T136" t="n">
         <v>4.551317153581415</v>
-      </c>
-      <c r="S136" t="n">
-        <v>2.866666666666666</v>
-      </c>
-      <c r="T136" t="n">
-        <v>1.433333333333333</v>
       </c>
       <c r="U136" t="n">
         <v>1.22759166992457</v>
@@ -13472,7 +13472,7 @@
         <v>1.51541667537397</v>
       </c>
       <c r="X136" t="n">
-        <v>5.89440283426485</v>
+        <v>5.894402834264851</v>
       </c>
       <c r="Y136" t="n">
         <v>3.937690752176724</v>
@@ -13540,22 +13540,22 @@
         <v>11.63</v>
       </c>
       <c r="O137" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P137" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q137" t="n">
         <v>39</v>
       </c>
-      <c r="P137" t="n">
+      <c r="R137" t="n">
         <v>2730</v>
       </c>
-      <c r="Q137" t="n">
+      <c r="S137" t="n">
         <v>78.14253905688253</v>
       </c>
-      <c r="R137" t="n">
+      <c r="T137" t="n">
         <v>9.339819828681623</v>
-      </c>
-      <c r="S137" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T137" t="n">
-        <v>2.3</v>
       </c>
       <c r="U137" t="n">
         <v>0.5376622777195503</v>
@@ -13635,22 +13635,22 @@
         <v>2.75</v>
       </c>
       <c r="O138" t="n">
+        <v>3.133333333333333</v>
+      </c>
+      <c r="P138" t="n">
+        <v>1.566666666666667</v>
+      </c>
+      <c r="Q138" t="n">
         <v>46.5</v>
       </c>
-      <c r="P138" t="n">
+      <c r="R138" t="n">
         <v>4557</v>
       </c>
-      <c r="Q138" t="n">
+      <c r="S138" t="n">
         <v>47.66031238193982</v>
       </c>
-      <c r="R138" t="n">
+      <c r="T138" t="n">
         <v>4.814418582676974</v>
-      </c>
-      <c r="S138" t="n">
-        <v>3.133333333333333</v>
-      </c>
-      <c r="T138" t="n">
-        <v>1.566666666666667</v>
       </c>
       <c r="U138" t="n">
         <v>1.154992622104217</v>
@@ -13730,22 +13730,22 @@
         <v>10.37</v>
       </c>
       <c r="O139" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P139" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q139" t="n">
         <v>65.8</v>
       </c>
-      <c r="P139" t="n">
+      <c r="R139" t="n">
         <v>11712.4</v>
       </c>
-      <c r="Q139" t="n">
+      <c r="S139" t="n">
         <v>51.28382196303994</v>
       </c>
-      <c r="R139" t="n">
+      <c r="T139" t="n">
         <v>3.843884969412038</v>
-      </c>
-      <c r="S139" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T139" t="n">
-        <v>1.1</v>
       </c>
       <c r="U139" t="n">
         <v>0.7256143706974467</v>
@@ -13825,22 +13825,22 @@
         <v>3.03</v>
       </c>
       <c r="O140" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="P140" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Q140" t="n">
         <v>58.7</v>
       </c>
-      <c r="P140" t="n">
+      <c r="R140" t="n">
         <v>6280.900000000001</v>
       </c>
-      <c r="Q140" t="n">
+      <c r="S140" t="n">
         <v>47.2486625825882</v>
       </c>
-      <c r="R140" t="n">
+      <c r="T140" t="n">
         <v>4.567700617719454</v>
-      </c>
-      <c r="S140" t="n">
-        <v>2.666666666666667</v>
-      </c>
-      <c r="T140" t="n">
-        <v>1.333333333333333</v>
       </c>
       <c r="U140" t="n">
         <v>1.229055584693399</v>
@@ -13920,22 +13920,22 @@
         <v>13.82</v>
       </c>
       <c r="O141" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P141" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q141" t="n">
         <v>25</v>
       </c>
-      <c r="P141" t="n">
+      <c r="R141" t="n">
         <v>2500</v>
       </c>
-      <c r="Q141" t="n">
+      <c r="S141" t="n">
         <v>92</v>
       </c>
-      <c r="R141" t="n">
+      <c r="T141" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="S141" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T141" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U141" t="n">
         <v>0.1345308929576061</v>
@@ -14015,22 +14015,22 @@
         <v>3.1</v>
       </c>
       <c r="O142" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P142" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q142" t="n">
         <v>25.5</v>
       </c>
-      <c r="P142" t="n">
+      <c r="R142" t="n">
         <v>2244</v>
       </c>
-      <c r="Q142" t="n">
+      <c r="S142" t="n">
         <v>100.7970198750255</v>
       </c>
-      <c r="R142" t="n">
+      <c r="T142" t="n">
         <v>10.74499842193307</v>
-      </c>
-      <c r="S142" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T142" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U142" t="n">
         <v>-0.02737119679613201</v>
@@ -14110,25 +14110,25 @@
         <v>12.31</v>
       </c>
       <c r="O143" t="n">
+        <v>3.133333333333333</v>
+      </c>
+      <c r="P143" t="n">
+        <v>1.566666666666667</v>
+      </c>
+      <c r="Q143" t="n">
         <v>29.8</v>
       </c>
-      <c r="P143" t="n">
+      <c r="R143" t="n">
         <v>1609.2</v>
       </c>
-      <c r="Q143" t="n">
+      <c r="S143" t="n">
         <v>70.70972897566557</v>
       </c>
-      <c r="R143" t="n">
+      <c r="T143" t="n">
         <v>9.62237532449285</v>
       </c>
-      <c r="S143" t="n">
-        <v>3.133333333333333</v>
-      </c>
-      <c r="T143" t="n">
-        <v>1.566666666666667</v>
-      </c>
       <c r="U143" t="n">
-        <v>0.4324315563379787</v>
+        <v>0.4324315563379786</v>
       </c>
       <c r="V143" t="n">
         <v>4.258583172709152</v>
@@ -14205,22 +14205,22 @@
         <v>8.94</v>
       </c>
       <c r="O144" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="P144" t="n">
+        <v>1.166666666666667</v>
+      </c>
+      <c r="Q144" t="n">
         <v>65.5</v>
       </c>
-      <c r="P144" t="n">
+      <c r="R144" t="n">
         <v>9039</v>
       </c>
-      <c r="Q144" t="n">
+      <c r="S144" t="n">
         <v>59.30899806866068</v>
       </c>
-      <c r="R144" t="n">
+      <c r="T144" t="n">
         <v>5.048717193870542</v>
-      </c>
-      <c r="S144" t="n">
-        <v>2.333333333333333</v>
-      </c>
-      <c r="T144" t="n">
-        <v>1.166666666666667</v>
       </c>
       <c r="U144" t="n">
         <v>0.7241612340891148</v>
@@ -14235,7 +14235,7 @@
         <v>6.173786103901937</v>
       </c>
       <c r="Y144" t="n">
-        <v>4.182050142641207</v>
+        <v>4.182050142641206</v>
       </c>
       <c r="Z144" t="n">
         <v>9.109303827798412</v>
@@ -14300,22 +14300,22 @@
         <v>5.69</v>
       </c>
       <c r="O145" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="P145" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="Q145" t="n">
         <v>59.8</v>
       </c>
-      <c r="P145" t="n">
+      <c r="R145" t="n">
         <v>6219.2</v>
       </c>
-      <c r="Q145" t="n">
+      <c r="S145" t="n">
         <v>47.9759206603761</v>
       </c>
-      <c r="R145" t="n">
+      <c r="T145" t="n">
         <v>4.704426069804557</v>
-      </c>
-      <c r="S145" t="n">
-        <v>4.666666666666666</v>
-      </c>
-      <c r="T145" t="n">
-        <v>2.333333333333333</v>
       </c>
       <c r="U145" t="n">
         <v>0.965080896043587</v>
@@ -14327,7 +14327,7 @@
         <v>1.548503782558456</v>
       </c>
       <c r="X145" t="n">
-        <v>5.916202062607435</v>
+        <v>5.916202062607436</v>
       </c>
       <c r="Y145" t="n">
         <v>4.091005660956586</v>
@@ -14395,22 +14395,22 @@
         <v>7.94</v>
       </c>
       <c r="O146" t="n">
+        <v>3.733333333333333</v>
+      </c>
+      <c r="P146" t="n">
+        <v>1.866666666666666</v>
+      </c>
+      <c r="Q146" t="n">
         <v>25</v>
       </c>
-      <c r="P146" t="n">
+      <c r="R146" t="n">
         <v>1775</v>
       </c>
-      <c r="Q146" t="n">
+      <c r="S146" t="n">
         <v>84.2</v>
       </c>
-      <c r="R146" t="n">
+      <c r="T146" t="n">
         <v>9.992701561992245</v>
-      </c>
-      <c r="S146" t="n">
-        <v>3.733333333333333</v>
-      </c>
-      <c r="T146" t="n">
-        <v>1.866666666666666</v>
       </c>
       <c r="U146" t="n">
         <v>0.3743183791113276</v>
@@ -14490,25 +14490,25 @@
         <v>2.83</v>
       </c>
       <c r="O147" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P147" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q147" t="n">
         <v>25</v>
       </c>
-      <c r="P147" t="n">
+      <c r="R147" t="n">
         <v>2000</v>
       </c>
-      <c r="Q147" t="n">
+      <c r="S147" t="n">
         <v>52.4</v>
       </c>
-      <c r="R147" t="n">
+      <c r="T147" t="n">
         <v>5.858498101049449</v>
       </c>
-      <c r="S147" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T147" t="n">
-        <v>1.1</v>
-      </c>
       <c r="U147" t="n">
-        <v>0.7561219797213338</v>
+        <v>0.7561219797213337</v>
       </c>
       <c r="V147" t="n">
         <v>3.958906591326997</v>
@@ -14585,22 +14585,22 @@
         <v>9.68</v>
       </c>
       <c r="O148" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="P148" t="n">
+        <v>1.633333333333333</v>
+      </c>
+      <c r="Q148" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="P148" t="n">
+      <c r="R148" t="n">
         <v>8205.6</v>
       </c>
-      <c r="Q148" t="n">
+      <c r="S148" t="n">
         <v>65.07127806801022</v>
       </c>
-      <c r="R148" t="n">
+      <c r="T148" t="n">
         <v>6.380763781600122</v>
-      </c>
-      <c r="S148" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="T148" t="n">
-        <v>1.633333333333333</v>
       </c>
       <c r="U148" t="n">
         <v>0.3708736633385454</v>
@@ -14680,22 +14680,22 @@
         <v>6.76</v>
       </c>
       <c r="O149" t="n">
+        <v>3.266666666666667</v>
+      </c>
+      <c r="P149" t="n">
+        <v>1.633333333333333</v>
+      </c>
+      <c r="Q149" t="n">
         <v>25</v>
       </c>
-      <c r="P149" t="n">
+      <c r="R149" t="n">
         <v>3325</v>
       </c>
-      <c r="Q149" t="n">
+      <c r="S149" t="n">
         <v>115.8</v>
       </c>
-      <c r="R149" t="n">
+      <c r="T149" t="n">
         <v>10.04113344708931</v>
-      </c>
-      <c r="S149" t="n">
-        <v>3.266666666666667</v>
-      </c>
-      <c r="T149" t="n">
-        <v>1.633333333333333</v>
       </c>
       <c r="U149" t="n">
         <v>0.03052920503482279</v>
@@ -14775,22 +14775,22 @@
         <v>5.49</v>
       </c>
       <c r="O150" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P150" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q150" t="n">
         <v>25</v>
       </c>
-      <c r="P150" t="n">
+      <c r="R150" t="n">
         <v>2200</v>
       </c>
-      <c r="Q150" t="n">
+      <c r="S150" t="n">
         <v>90.2</v>
       </c>
-      <c r="R150" t="n">
+      <c r="T150" t="n">
         <v>9.61535230763803</v>
-      </c>
-      <c r="S150" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T150" t="n">
-        <v>1.6</v>
       </c>
       <c r="U150" t="n">
         <v>0.3089542077273207</v>
@@ -14802,7 +14802,7 @@
         <v>2.263361019829475</v>
       </c>
       <c r="X150" t="n">
-        <v>6.111467339502679</v>
+        <v>6.111467339502678</v>
       </c>
       <c r="Y150" t="n">
         <v>3.218875824868201</v>
@@ -14870,22 +14870,22 @@
         <v>3.76</v>
       </c>
       <c r="O151" t="n">
+        <v>2.866666666666666</v>
+      </c>
+      <c r="P151" t="n">
+        <v>1.433333333333333</v>
+      </c>
+      <c r="Q151" t="n">
         <v>25</v>
       </c>
-      <c r="P151" t="n">
+      <c r="R151" t="n">
         <v>3200</v>
       </c>
-      <c r="Q151" t="n">
+      <c r="S151" t="n">
         <v>87.40000000000001</v>
       </c>
-      <c r="R151" t="n">
+      <c r="T151" t="n">
         <v>7.725141584463032</v>
-      </c>
-      <c r="S151" t="n">
-        <v>2.866666666666666</v>
-      </c>
-      <c r="T151" t="n">
-        <v>1.433333333333333</v>
       </c>
       <c r="U151" t="n">
         <v>-0.04395188752918283</v>
@@ -14965,22 +14965,22 @@
         <v>18.47</v>
       </c>
       <c r="O152" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P152" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q152" t="n">
         <v>49.7</v>
       </c>
-      <c r="P152" t="n">
+      <c r="R152" t="n">
         <v>2037.7</v>
       </c>
-      <c r="Q152" t="n">
+      <c r="S152" t="n">
         <v>76.59767110895667</v>
       </c>
-      <c r="R152" t="n">
+      <c r="T152" t="n">
         <v>11.96254644899196</v>
-      </c>
-      <c r="S152" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T152" t="n">
-        <v>1.4</v>
       </c>
       <c r="U152" t="n">
         <v>0.3555743384946994</v>
@@ -15060,22 +15060,22 @@
         <v>3.37</v>
       </c>
       <c r="O153" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="P153" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Q153" t="n">
         <v>37.1</v>
       </c>
-      <c r="P153" t="n">
+      <c r="R153" t="n">
         <v>3227.7</v>
       </c>
-      <c r="Q153" t="n">
+      <c r="S153" t="n">
         <v>68.62610129517589</v>
       </c>
-      <c r="R153" t="n">
+      <c r="T153" t="n">
         <v>7.357490341560629</v>
-      </c>
-      <c r="S153" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="T153" t="n">
-        <v>1.666666666666667</v>
       </c>
       <c r="U153" t="n">
         <v>0.3492474281099357</v>
@@ -15155,22 +15155,22 @@
         <v>12.26</v>
       </c>
       <c r="O154" t="n">
+        <v>4</v>
+      </c>
+      <c r="P154" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q154" t="n">
         <v>53.7</v>
       </c>
-      <c r="P154" t="n">
+      <c r="R154" t="n">
         <v>5477.400000000001</v>
       </c>
-      <c r="Q154" t="n">
+      <c r="S154" t="n">
         <v>56.90480141939699</v>
       </c>
-      <c r="R154" t="n">
+      <c r="T154" t="n">
         <v>5.63441493089915</v>
-      </c>
-      <c r="S154" t="n">
-        <v>4</v>
-      </c>
-      <c r="T154" t="n">
-        <v>2</v>
       </c>
       <c r="U154" t="n">
         <v>0.676509539406922</v>
@@ -15250,25 +15250,25 @@
         <v>11.7</v>
       </c>
       <c r="O155" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P155" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q155" t="n">
         <v>47.6</v>
       </c>
-      <c r="P155" t="n">
+      <c r="R155" t="n">
         <v>5236</v>
       </c>
-      <c r="Q155" t="n">
+      <c r="S155" t="n">
         <v>72.76126497438227</v>
       </c>
-      <c r="R155" t="n">
+      <c r="T155" t="n">
         <v>6.937514409925916</v>
       </c>
-      <c r="S155" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T155" t="n">
-        <v>1.4</v>
-      </c>
       <c r="U155" t="n">
-        <v>0.2255406759139312</v>
+        <v>0.2255406759139311</v>
       </c>
       <c r="V155" t="n">
         <v>4.287183739073042</v>
@@ -15280,7 +15280,7 @@
         <v>6.218600119691729</v>
       </c>
       <c r="Y155" t="n">
-        <v>3.862832761237375</v>
+        <v>3.862832761237374</v>
       </c>
       <c r="Z155" t="n">
         <v>8.56331312702979</v>
@@ -15345,22 +15345,22 @@
         <v>11.1</v>
       </c>
       <c r="O156" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P156" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q156" t="n">
         <v>50</v>
       </c>
-      <c r="P156" t="n">
+      <c r="R156" t="n">
         <v>3550</v>
       </c>
-      <c r="Q156" t="n">
+      <c r="S156" t="n">
         <v>57.55849198858497</v>
       </c>
-      <c r="R156" t="n">
+      <c r="T156" t="n">
         <v>6.830936256535049</v>
-      </c>
-      <c r="S156" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T156" t="n">
-        <v>1.8</v>
       </c>
       <c r="U156" t="n">
         <v>0.9454611091739349</v>
@@ -15440,22 +15440,22 @@
         <v>6.64</v>
       </c>
       <c r="O157" t="n">
+        <v>3.066666666666666</v>
+      </c>
+      <c r="P157" t="n">
+        <v>1.533333333333333</v>
+      </c>
+      <c r="Q157" t="n">
         <v>67.2</v>
       </c>
-      <c r="P157" t="n">
+      <c r="R157" t="n">
         <v>3696</v>
       </c>
-      <c r="Q157" t="n">
+      <c r="S157" t="n">
         <v>49.52692870213806</v>
       </c>
-      <c r="R157" t="n">
+      <c r="T157" t="n">
         <v>6.678209703841655</v>
-      </c>
-      <c r="S157" t="n">
-        <v>3.066666666666666</v>
-      </c>
-      <c r="T157" t="n">
-        <v>1.533333333333333</v>
       </c>
       <c r="U157" t="n">
         <v>0.9162907318741551</v>
@@ -15535,22 +15535,22 @@
         <v>10.03</v>
       </c>
       <c r="O158" t="n">
+        <v>3.866666666666666</v>
+      </c>
+      <c r="P158" t="n">
+        <v>1.933333333333333</v>
+      </c>
+      <c r="Q158" t="n">
         <v>38.3</v>
       </c>
-      <c r="P158" t="n">
+      <c r="R158" t="n">
         <v>4442.799999999999</v>
       </c>
-      <c r="Q158" t="n">
+      <c r="S158" t="n">
         <v>56.39310922110982</v>
       </c>
-      <c r="R158" t="n">
+      <c r="T158" t="n">
         <v>5.235968743834705</v>
-      </c>
-      <c r="S158" t="n">
-        <v>3.866666666666666</v>
-      </c>
-      <c r="T158" t="n">
-        <v>1.933333333333333</v>
       </c>
       <c r="U158" t="n">
         <v>0.6585557357903262</v>
@@ -15630,25 +15630,25 @@
         <v>8.050000000000001</v>
       </c>
       <c r="O159" t="n">
+        <v>3.133333333333333</v>
+      </c>
+      <c r="P159" t="n">
+        <v>1.566666666666667</v>
+      </c>
+      <c r="Q159" t="n">
         <v>63.3</v>
       </c>
-      <c r="P159" t="n">
+      <c r="R159" t="n">
         <v>2532</v>
       </c>
-      <c r="Q159" t="n">
+      <c r="S159" t="n">
         <v>72.6483882108657</v>
       </c>
-      <c r="R159" t="n">
+      <c r="T159" t="n">
         <v>11.48671875432302</v>
       </c>
-      <c r="S159" t="n">
-        <v>3.133333333333333</v>
-      </c>
-      <c r="T159" t="n">
-        <v>1.566666666666667</v>
-      </c>
       <c r="U159" t="n">
-        <v>0.6444820085786642</v>
+        <v>0.6444820085786643</v>
       </c>
       <c r="V159" t="n">
         <v>4.285631204097312</v>
@@ -15725,22 +15725,22 @@
         <v>9.99</v>
       </c>
       <c r="O160" t="n">
+        <v>3</v>
+      </c>
+      <c r="P160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q160" t="n">
         <v>40.9</v>
       </c>
-      <c r="P160" t="n">
+      <c r="R160" t="n">
         <v>5276.099999999999</v>
       </c>
-      <c r="Q160" t="n">
+      <c r="S160" t="n">
         <v>45.65845350565564</v>
       </c>
-      <c r="R160" t="n">
+      <c r="T160" t="n">
         <v>4.020002677048086</v>
-      </c>
-      <c r="S160" t="n">
-        <v>3</v>
-      </c>
-      <c r="T160" t="n">
-        <v>1.5</v>
       </c>
       <c r="U160" t="n">
         <v>1.383289852099592</v>
@@ -15820,22 +15820,22 @@
         <v>5.97</v>
       </c>
       <c r="O161" t="n">
+        <v>4.533333333333333</v>
+      </c>
+      <c r="P161" t="n">
+        <v>2.266666666666667</v>
+      </c>
+      <c r="Q161" t="n">
         <v>44.9</v>
       </c>
-      <c r="P161" t="n">
+      <c r="R161" t="n">
         <v>4310.4</v>
       </c>
-      <c r="Q161" t="n">
+      <c r="S161" t="n">
         <v>48.20358644439695</v>
       </c>
-      <c r="R161" t="n">
+      <c r="T161" t="n">
         <v>4.919757940038025</v>
-      </c>
-      <c r="S161" t="n">
-        <v>4.533333333333333</v>
-      </c>
-      <c r="T161" t="n">
-        <v>2.266666666666667</v>
       </c>
       <c r="U161" t="n">
         <v>1.293630676256471</v>
@@ -15915,22 +15915,22 @@
         <v>12.57</v>
       </c>
       <c r="O162" t="n">
+        <v>4.666666666666666</v>
+      </c>
+      <c r="P162" t="n">
+        <v>2.333333333333333</v>
+      </c>
+      <c r="Q162" t="n">
         <v>45.9</v>
       </c>
-      <c r="P162" t="n">
+      <c r="R162" t="n">
         <v>2340.9</v>
       </c>
-      <c r="Q162" t="n">
+      <c r="S162" t="n">
         <v>73.65363798075126</v>
       </c>
-      <c r="R162" t="n">
+      <c r="T162" t="n">
         <v>10.3135722380655</v>
-      </c>
-      <c r="S162" t="n">
-        <v>4.666666666666666</v>
-      </c>
-      <c r="T162" t="n">
-        <v>2.333333333333333</v>
       </c>
       <c r="U162" t="n">
         <v>0.2452963559553431</v>
@@ -16010,22 +16010,22 @@
         <v>2.86</v>
       </c>
       <c r="O163" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P163" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q163" t="n">
         <v>40.9</v>
       </c>
-      <c r="P163" t="n">
+      <c r="R163" t="n">
         <v>4130.9</v>
       </c>
-      <c r="Q163" t="n">
+      <c r="S163" t="n">
         <v>55.66578578086783</v>
       </c>
-      <c r="R163" t="n">
+      <c r="T163" t="n">
         <v>5.538952707422589</v>
-      </c>
-      <c r="S163" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T163" t="n">
-        <v>1.8</v>
       </c>
       <c r="U163" t="n">
         <v>0.8232978650249904</v>
@@ -16105,22 +16105,22 @@
         <v>4.86</v>
       </c>
       <c r="O164" t="n">
+        <v>4.199999999999999</v>
+      </c>
+      <c r="P164" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q164" t="n">
         <v>43.7</v>
       </c>
-      <c r="P164" t="n">
+      <c r="R164" t="n">
         <v>7341.6</v>
       </c>
-      <c r="Q164" t="n">
+      <c r="S164" t="n">
         <v>71.55177671149809</v>
       </c>
-      <c r="R164" t="n">
+      <c r="T164" t="n">
         <v>5.520339421161875</v>
-      </c>
-      <c r="S164" t="n">
-        <v>4.199999999999999</v>
-      </c>
-      <c r="T164" t="n">
-        <v>2.1</v>
       </c>
       <c r="U164" t="n">
         <v>0.6333971761541712</v>
@@ -16200,22 +16200,22 @@
         <v>7.62</v>
       </c>
       <c r="O165" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P165" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q165" t="n">
         <v>31.6</v>
       </c>
-      <c r="P165" t="n">
+      <c r="R165" t="n">
         <v>4834.8</v>
       </c>
-      <c r="Q165" t="n">
+      <c r="S165" t="n">
         <v>57.45912140740921</v>
       </c>
-      <c r="R165" t="n">
+      <c r="T165" t="n">
         <v>4.645294641528179</v>
-      </c>
-      <c r="S165" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T165" t="n">
-        <v>1.4</v>
       </c>
       <c r="U165" t="n">
         <v>0.859085258103376</v>
